--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z833"/>
+  <dimension ref="A1:Z834"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44322</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>44761</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>45204</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44221</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>44937</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45084</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45162</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>44000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44435</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>45013</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45196</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45239</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>43452</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>43510</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44188</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45099</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>43872</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44322</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44480</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>44831</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>44998</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>45061</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45121</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45211</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>43389</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>43453</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>43581</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>43873</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44167</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44188</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44410</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44456</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44547</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>44560</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44571</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44693</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44694</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>44706</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44825</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44832</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44874</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>44888</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45035</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>45041</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45089</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45093</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45126</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>45140</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>45153</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45189</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45197</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45208</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>43355</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>43363</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>43385</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>43385</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>43389</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>43389</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43403</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>43404</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>43404</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>43404</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>43411</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>43413</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>43416</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>43425</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>43427</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>43436</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>43447</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>43451</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>43452</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>43472</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>43472</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>43472</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>43473</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>43474</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>43494</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>43497</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>43500</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>43501</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>43502</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43531</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>43532</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>43546</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>43551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>43557</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>43566</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>43593</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>43594</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>43601</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>43605</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>43614</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>43628</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43630</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43630</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43633</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>43649</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>43656</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>43662</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>43664</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>43681</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>43705</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>43714</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43720</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>43731</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>43733</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>43734</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43747</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43770</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43780</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43782</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43788</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43791</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>43797</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>43798</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>43798</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>43798</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>43798</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43801</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43817</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43819</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43847</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43847</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43858</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>43860</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43861</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>43861</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>43868</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>43868</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>43872</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>43873</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>43881</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>43881</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>43882</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>43887</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>43887</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>43892</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>43892</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43893</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43893</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43894</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>43894</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>43895</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>43898</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>43900</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>43903</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>43903</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>43908</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>43910</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>43915</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>43918</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>43921</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>43921</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>43922</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>43923</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>43923</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43923</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43923</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>43923</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>43923</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>43924</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>43949</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43965</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>43965</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>43969</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>43978</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>43983</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>43983</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>43983</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>43983</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43983</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43993</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43999</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44000</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44000</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44006</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44012</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44020</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>44022</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>44036</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44067</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44069</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>44069</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44070</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44081</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44085</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44085</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44085</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44085</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44089</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44090</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44092</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44092</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44092</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44092</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44092</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44092</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44092</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>44093</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>44097</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>44097</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>44103</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44103</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>44104</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>44113</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44116</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44116</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>44118</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44119</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44119</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44120</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44123</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>44124</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>44127</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44127</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44131</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44154</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44154</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44154</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44154</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>44159</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44165</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44166</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>44168</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44174</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44188</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44188</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44188</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44188</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44188</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44209</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44217</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44218</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44224</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>44237</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44244</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>44244</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>44249</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>44264</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>44274</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44281</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>44286</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44291</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>44292</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>44292</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44299</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>44302</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>44316</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>44316</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>44316</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44316</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44316</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44322</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44322</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44322</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44330</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44333</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44336</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>44336</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>44337</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>44341</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44344</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44344</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>44358</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44362</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>44364</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>44368</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>44369</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>44369</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>44370</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>44370</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44370</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44370</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44376</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>44377</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>44377</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44386</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44386</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>44387</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>44393</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44397</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44404</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44405</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44406</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>44413</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>44431</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44434</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44435</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44435</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44439</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>44439</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>44441</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44447</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44449</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44452</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44453</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>44456</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>44456</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44459</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>44459</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>44460</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44462</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44470</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>44476</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44477</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44477</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44482</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44482</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>44502</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>44503</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44508</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>44516</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44533</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>44536</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44543</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44550</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>44552</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44560</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>44560</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44572</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44579</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44579</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44581</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44590</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>44599</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>44600</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44602</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44603</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44616</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44643</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44652</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44656</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>44658</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>44662</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44680</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>44685</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44687</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>44687</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>44700</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44701</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>44706</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44706</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44708</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44711</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44715</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44720</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44720</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44725</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>44729</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44730</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44730</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44730</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44730</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44731</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44731</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44731</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44731</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44731</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44731</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44731</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44731</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>44730</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44731</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>44731</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>44731</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>44731</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44732</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>44733</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44741</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44743</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44771</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>44771</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>44771</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44785</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44789</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44805</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44805</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44809</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44809</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44811</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>44813</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44817</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>44817</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>44819</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>44820</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>44820</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>44820</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>44825</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>44825</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>44825</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44826</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44826</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44827</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44827</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44827</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>44827</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>44830</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>44831</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44831</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44831</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44832</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44833</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44833</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44841</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44844</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44844</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44844</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44844</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44844</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44845</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>44848</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44851</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44851</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44853</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44854</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44859</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>44859</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44859</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>44859</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>44859</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>44859</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>44859</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44861</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44862</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44865</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>44867</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>44867</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>44869</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44869</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44869</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>44872</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44872</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44872</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>44872</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44874</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>44879</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>44879</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>44879</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>44880</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>44883</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44883</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44886</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44887</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44890</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44890</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44893</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44893</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44893</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44895</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>44903</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44907</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>44907</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44915</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44915</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44915</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44916</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44923</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>44929</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>44929</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44929</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>44937</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44938</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>44939</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>44942</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>44950</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44957</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>44957</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44958</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>44958</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44960</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44960</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44960</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44960</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44960</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44964</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>44965</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44966</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44967</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>44970</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44970</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>44970</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44971</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44972</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44974</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>44978</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>44981</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>44994</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>44994</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>44998</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45002</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45002</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45002</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45013</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45021</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45030</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45034</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45034</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45034</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45034</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45043</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>45043</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>45043</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45044</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45044</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>45044</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45056</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45058</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45058</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45058</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45062</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45062</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45062</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45062</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45063</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45063</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45063</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45063</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45063</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45063</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45063</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45063</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45068</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45068</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45068</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45068</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45068</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45069</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45069</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45070</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45070</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45070</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45070</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45071</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45078</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45079</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45079</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45082</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45082</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45084</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45086</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45086</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>45089</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>45091</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>45093</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45093</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45098</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45098</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45098</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45098</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45099</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45099</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45099</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45099</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45099</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45105</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>45105</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>45106</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45107</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45107</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45110</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45110</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45110</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45110</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45112</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45112</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>45112</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45113</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45113</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45114</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45114</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>45114</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45114</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45117</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45118</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45119</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45119</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45119</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>45121</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45121</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45125</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45125</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45125</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45126</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45127</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45128</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45128</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45128</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>45131</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>45131</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45132</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>45134</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45134</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45134</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45134</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45134</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45135</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45140</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45140</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45142</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>45148</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45149</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45149</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45149</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45152</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45152</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>45152</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45155</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45156</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45156</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45156</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>45156</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45156</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45161</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45161</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45161</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45161</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45161</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45163</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>45163</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>45166</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45166</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45166</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45166</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45167</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45167</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45167</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45167</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45168</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45168</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45168</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45168</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>45168</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45168</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45170</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45170</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45170</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45173</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45174</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45175</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45175</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43654,7 +43654,7 @@
         <v>45175</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45176</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45177</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45177</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45177</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45177</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45177</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45180</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45180</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45182</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>45182</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45182</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45183</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45184</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45184</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45184</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45187</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45187</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45187</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45187</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45187</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>45187</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45188</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45188</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45188</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>45188</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>45188</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45189</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45191</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45191</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45191</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45191</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>45191</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45191</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>45194</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>45195</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45196</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45196</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45198</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45198</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>45198</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45198</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45198</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45198</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45198</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45198</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45198</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45202</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45202</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>45202</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45202</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45204</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45204</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45205</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45205</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>45205</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>45205</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45208</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>45210</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47840,7 +47840,7 @@
         <v>45212</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45212</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45215</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45215</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45216</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45217</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>45218</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>45219</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45219</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45219</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45219</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45223</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45224</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>45225</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45225</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45225</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45225</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45226</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45226</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45226</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45230</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45230</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45230</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45230</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45230</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45236</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>45236</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>45237</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>45239</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>45243</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45243</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45243</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45244</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50002,7 +50002,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45247</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50121,7 +50121,7 @@
         <v>45247</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45247</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45249</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45253</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45253</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45253</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45253</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>45254</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45257</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45257</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45257</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45260</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45265</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45273</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45280</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51254,7 +51254,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51368,7 +51368,7 @@
         <v>45288</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45297</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>45301</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51601,7 +51601,7 @@
         <v>45301</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51658,7 +51658,7 @@
         <v>45302</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45303</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>45307</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45308</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51884,14 +51884,14 @@
     <row r="824" ht="15" customHeight="1">
       <c r="A824" t="inlineStr">
         <is>
-          <t>A 2484-2024</t>
+          <t>A 2481-2024</t>
         </is>
       </c>
       <c r="B824" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         </is>
       </c>
       <c r="G824" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -51937,18 +51937,38 @@
         <v>0</v>
       </c>
       <c r="R824" s="2" t="inlineStr"/>
+      <c r="U824">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/knärot/A 2481-2024 karta knärot.png", "A 2481-2024")</f>
+        <v/>
+      </c>
+      <c r="V824">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomål/A 2481-2024 FSC-klagomål.docx", "A 2481-2024")</f>
+        <v/>
+      </c>
+      <c r="W824">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomålsmail/A 2481-2024 FSC-klagomål mail.docx", "A 2481-2024")</f>
+        <v/>
+      </c>
+      <c r="X824">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsyn/A 2481-2024 tillsynsbegäran.docx", "A 2481-2024")</f>
+        <v/>
+      </c>
+      <c r="Y824">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsynsmail/A 2481-2024 tillsynsbegäran mail.docx", "A 2481-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="825" ht="15" customHeight="1">
       <c r="A825" t="inlineStr">
         <is>
-          <t>A 2603-2024</t>
+          <t>A 2485-2024</t>
         </is>
       </c>
       <c r="B825" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51961,7 +51981,7 @@
         </is>
       </c>
       <c r="G825" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="H825" t="n">
         <v>0</v>
@@ -51998,14 +52018,14 @@
     <row r="826" ht="15" customHeight="1">
       <c r="A826" t="inlineStr">
         <is>
-          <t>A 2481-2024</t>
+          <t>A 2484-2024</t>
         </is>
       </c>
       <c r="B826" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52018,7 +52038,7 @@
         </is>
       </c>
       <c r="G826" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="H826" t="n">
         <v>0</v>
@@ -52051,38 +52071,18 @@
         <v>0</v>
       </c>
       <c r="R826" s="2" t="inlineStr"/>
-      <c r="U826">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2085/knärot/A 2481-2024 karta knärot.png", "A 2481-2024")</f>
-        <v/>
-      </c>
-      <c r="V826">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomål/A 2481-2024 FSC-klagomål.docx", "A 2481-2024")</f>
-        <v/>
-      </c>
-      <c r="W826">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomålsmail/A 2481-2024 FSC-klagomål mail.docx", "A 2481-2024")</f>
-        <v/>
-      </c>
-      <c r="X826">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsyn/A 2481-2024 tillsynsbegäran.docx", "A 2481-2024")</f>
-        <v/>
-      </c>
-      <c r="Y826">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsynsmail/A 2481-2024 tillsynsbegäran mail.docx", "A 2481-2024")</f>
-        <v/>
-      </c>
     </row>
     <row r="827" ht="15" customHeight="1">
       <c r="A827" t="inlineStr">
         <is>
-          <t>A 2485-2024</t>
+          <t>A 2603-2024</t>
         </is>
       </c>
       <c r="B827" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         </is>
       </c>
       <c r="G827" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="H827" t="n">
         <v>0</v>
@@ -52139,7 +52139,7 @@
         <v>45317</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>45317</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52253,7 +52253,7 @@
         <v>45321</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52310,7 +52310,7 @@
         <v>45321</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52367,7 +52367,7 @@
         <v>45334</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52414,7 +52414,7 @@
       </c>
       <c r="R832" s="2" t="inlineStr"/>
     </row>
-    <row r="833">
+    <row r="833" ht="15" customHeight="1">
       <c r="A833" t="inlineStr">
         <is>
           <t>A 5841-2024</t>
@@ -52424,7 +52424,7 @@
         <v>45335</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52470,6 +52470,63 @@
         <v>0</v>
       </c>
       <c r="R833" s="2" t="inlineStr"/>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>A 6151-2024</t>
+        </is>
+      </c>
+      <c r="B834" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C834" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="G834" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H834" t="n">
+        <v>0</v>
+      </c>
+      <c r="I834" t="n">
+        <v>0</v>
+      </c>
+      <c r="J834" t="n">
+        <v>0</v>
+      </c>
+      <c r="K834" t="n">
+        <v>0</v>
+      </c>
+      <c r="L834" t="n">
+        <v>0</v>
+      </c>
+      <c r="M834" t="n">
+        <v>0</v>
+      </c>
+      <c r="N834" t="n">
+        <v>0</v>
+      </c>
+      <c r="O834" t="n">
+        <v>0</v>
+      </c>
+      <c r="P834" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q834" t="n">
+        <v>0</v>
+      </c>
+      <c r="R834" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -569,7 +569,7 @@
         <v>44322</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>44761</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>45204</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44221</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>44937</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45084</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45162</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>44000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44435</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>45013</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45196</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45239</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>43452</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>43510</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44188</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45099</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>43872</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44322</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44480</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>44831</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>44998</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>45061</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45121</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45211</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>43389</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>43453</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>43581</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>43873</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44167</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44188</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44410</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44456</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44547</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>44560</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44571</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44693</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44694</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>44706</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44825</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44832</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44874</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>44888</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45035</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>45041</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45089</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45093</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45126</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>45140</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>45153</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45189</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45197</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45208</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>43355</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>43363</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>43385</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>43385</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>43389</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>43389</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43403</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>43404</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>43404</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>43404</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>43411</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>43413</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>43416</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>43425</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>43427</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>43436</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>43447</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>43451</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>43452</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>43472</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>43472</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>43472</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>43473</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>43474</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>43494</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>43497</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>43500</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>43501</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>43502</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43531</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>43532</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>43546</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>43551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>43557</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>43566</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>43593</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>43594</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>43601</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>43605</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>43614</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>43628</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43630</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43630</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43633</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>43649</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>43656</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>43662</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>43664</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>43681</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>43705</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>43714</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43720</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>43731</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>43733</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>43734</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43747</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43770</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43780</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43782</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43788</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43791</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>43797</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>43798</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>43798</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>43798</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>43798</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43801</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43817</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43819</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43847</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43847</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43858</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>43860</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43861</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>43861</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>43868</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>43868</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>43872</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>43873</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>43881</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>43881</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>43882</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>43887</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>43887</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>43892</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>43892</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43893</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43893</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43894</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>43894</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>43895</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>43898</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>43900</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>43903</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>43903</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>43908</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>43910</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>43915</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>43918</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>43921</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>43921</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>43922</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>43923</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>43923</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43923</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43923</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>43923</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>43923</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>43924</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>43949</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43965</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>43965</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>43969</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>43978</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>43983</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>43983</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>43983</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>43983</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43983</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43993</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43999</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44000</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44000</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44006</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44012</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44020</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>44022</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>44036</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44067</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44069</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>44069</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44070</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44081</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44085</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44085</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44085</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44085</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44089</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44090</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44092</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44092</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44092</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44092</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44092</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44092</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44092</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>44093</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>44097</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>44097</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>44103</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44103</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>44104</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>44113</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44116</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44116</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>44118</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44119</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44119</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44120</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44123</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>44124</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>44127</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44127</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44131</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44154</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44154</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44154</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44154</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>44159</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44165</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44166</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>44168</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44174</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44188</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44188</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44188</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44188</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44188</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44209</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44217</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44218</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44224</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>44237</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44244</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>44244</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>44249</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>44264</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>44274</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44281</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>44286</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44291</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>44292</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>44292</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44299</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>44302</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>44316</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>44316</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>44316</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44316</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44316</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44322</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44322</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44322</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44330</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44333</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44336</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>44336</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>44337</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>44341</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44344</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44344</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>44358</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44362</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>44364</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>44368</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>44369</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>44369</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>44370</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>44370</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44370</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44370</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44376</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>44377</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>44377</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44386</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44386</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>44387</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>44393</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44397</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44404</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44405</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44406</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>44413</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>44431</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44434</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44435</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44435</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44439</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>44439</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>44441</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44447</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44449</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44452</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44453</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>44456</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>44456</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44459</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>44459</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>44460</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44462</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44470</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>44476</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44477</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44477</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44482</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44482</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>44502</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>44503</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44508</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>44516</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44533</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>44536</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44543</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44550</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>44552</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44560</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>44560</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44572</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44579</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44579</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44581</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44590</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>44599</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>44600</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44602</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44603</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44616</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44643</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44652</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44656</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>44658</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>44662</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44680</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>44685</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44687</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>44687</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>44700</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44701</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>44706</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44706</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44708</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44711</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44715</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44720</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44720</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44725</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>44729</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44730</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44730</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44730</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44730</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44731</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44731</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44731</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44731</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44731</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44731</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44731</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44731</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>44730</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44731</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>44731</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>44731</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>44731</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44732</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>44733</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44741</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44743</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44771</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>44771</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>44771</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44785</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44789</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44805</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44805</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44809</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44809</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44811</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>44813</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44817</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>44817</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>44819</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>44820</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>44820</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>44820</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>44825</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>44825</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>44825</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44826</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44826</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44827</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44827</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44827</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>44827</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>44830</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>44831</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44831</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44831</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44832</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44833</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44833</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44841</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44844</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44844</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44844</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44844</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44844</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44845</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>44848</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44851</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44851</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44853</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44854</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44859</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>44859</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44859</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>44859</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>44859</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>44859</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>44859</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44861</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44862</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44865</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>44867</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>44867</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>44869</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44869</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44869</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>44872</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44872</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44872</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>44872</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44874</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>44879</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>44879</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>44879</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>44880</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>44883</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44883</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44886</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44887</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44890</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44890</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44893</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44893</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44893</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44895</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>44903</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44907</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>44907</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44915</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44915</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44915</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44916</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44923</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>44929</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>44929</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44929</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>44937</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44938</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>44939</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>44942</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>44950</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44957</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>44957</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44958</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>44958</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44960</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44960</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44960</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44960</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44960</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44964</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>44965</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44966</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44967</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>44970</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44970</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>44970</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44971</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44972</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44974</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>44978</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>44981</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>44994</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>44994</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>44998</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45002</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45002</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45002</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45013</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45021</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45030</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45034</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45034</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45034</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45034</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45043</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>45043</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>45043</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45044</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45044</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>45044</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45056</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45058</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45058</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45058</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45062</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45062</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45062</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45062</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45063</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45063</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45063</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45063</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45063</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45063</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45063</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45063</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45068</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45068</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45068</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45068</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45068</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45069</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45069</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45070</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45070</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45070</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45070</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45071</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45078</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45079</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45079</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45082</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45082</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45084</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45086</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45086</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>45089</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>45091</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>45093</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45093</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45098</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45098</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45098</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45098</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45099</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45099</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45099</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45099</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45099</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45105</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>45105</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>45106</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45107</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45107</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45110</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45110</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45110</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45110</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45112</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45112</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>45112</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45113</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45113</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45114</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45114</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>45114</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45114</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45117</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45118</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45119</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45119</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45119</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>45121</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45121</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45125</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45125</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45125</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45126</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45127</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45128</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45128</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45128</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>45131</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>45131</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45132</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>45134</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45134</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45134</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45134</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45134</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45135</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45140</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45140</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45142</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>45148</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45149</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45149</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45149</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45152</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45152</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>45152</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45155</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45156</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45156</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45156</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>45156</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45156</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45161</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45161</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45161</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45161</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45161</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45163</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>45163</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>45166</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45166</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45166</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45166</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45167</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45167</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45167</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45167</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45168</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45168</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45168</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45168</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>45168</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45168</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45170</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45170</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45170</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45173</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45174</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45175</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45175</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43654,7 +43654,7 @@
         <v>45175</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45176</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45177</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45177</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45177</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45177</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45177</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45180</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45180</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45182</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>45182</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45182</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45183</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45184</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45184</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45184</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45187</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45187</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45187</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45187</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45187</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>45187</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45188</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45188</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45188</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>45188</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>45188</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45189</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45191</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45191</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45191</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45191</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>45191</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45191</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>45194</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>45195</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45196</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45196</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45198</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45198</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>45198</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45198</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45198</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45198</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45198</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45198</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45198</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45202</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45202</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>45202</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45202</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45204</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45204</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45205</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45205</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>45205</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>45205</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45208</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>45210</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47840,7 +47840,7 @@
         <v>45212</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45212</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45215</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45215</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45216</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45217</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>45218</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>45219</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45219</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45219</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45219</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45223</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45224</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>45225</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45225</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45225</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45225</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45226</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45226</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45226</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45230</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45230</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45230</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45230</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45230</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45236</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>45236</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>45237</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>45239</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>45243</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45243</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45243</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45244</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50002,7 +50002,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45247</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50121,7 +50121,7 @@
         <v>45247</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45247</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45249</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45253</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45253</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45253</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45253</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>45254</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45257</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45257</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45257</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45260</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45265</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45273</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45280</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51254,7 +51254,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51368,7 +51368,7 @@
         <v>45288</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45297</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>45301</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51601,7 +51601,7 @@
         <v>45301</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51658,7 +51658,7 @@
         <v>45302</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45303</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>45307</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45308</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45313</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45313</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45313</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>45313</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52132,14 +52132,14 @@
     <row r="828" ht="15" customHeight="1">
       <c r="A828" t="inlineStr">
         <is>
-          <t>A 3277-2024</t>
+          <t>A 3280-2024</t>
         </is>
       </c>
       <c r="B828" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         </is>
       </c>
       <c r="G828" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -52189,14 +52189,14 @@
     <row r="829" ht="15" customHeight="1">
       <c r="A829" t="inlineStr">
         <is>
-          <t>A 3280-2024</t>
+          <t>A 3277-2024</t>
         </is>
       </c>
       <c r="B829" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         </is>
       </c>
       <c r="G829" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -52253,7 +52253,7 @@
         <v>45321</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52310,7 +52310,7 @@
         <v>45321</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52367,7 +52367,7 @@
         <v>45334</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         <v>45335</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45337</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z834"/>
+  <dimension ref="A1:Z836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44322</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>44761</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>45204</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44221</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>44937</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45084</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45162</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>44000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44435</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>45013</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45196</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45239</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>43452</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>43510</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44188</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45099</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>43872</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44322</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44480</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>44831</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>44998</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>45061</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45121</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45211</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>43389</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>43453</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>43581</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>43873</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44167</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44188</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44410</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44456</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44547</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>44560</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44571</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44693</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44694</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>44706</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44825</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44832</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44874</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>44888</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45035</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>45041</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45089</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45093</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45126</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>45140</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>45153</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45189</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45197</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45208</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>43355</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>43363</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>43385</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>43385</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>43389</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>43389</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43403</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>43404</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>43404</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>43404</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>43411</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>43413</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>43416</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>43425</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>43427</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>43436</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>43447</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>43451</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>43452</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>43472</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>43472</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>43472</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>43473</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>43474</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>43494</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>43497</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>43500</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>43501</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>43502</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43531</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>43532</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>43546</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>43551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>43557</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>43566</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>43593</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>43594</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>43601</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>43605</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>43614</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>43628</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43630</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43630</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43633</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>43649</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>43656</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>43662</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>43664</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>43681</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>43705</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>43714</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43720</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>43731</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>43733</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>43734</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43747</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43770</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43780</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43782</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43788</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43791</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>43797</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>43798</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>43798</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>43798</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>43798</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43801</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43817</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43819</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43847</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43847</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43858</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>43860</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43861</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>43861</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>43868</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>43868</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>43872</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>43873</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>43881</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>43881</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>43882</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>43887</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>43887</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>43892</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>43892</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43893</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43893</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43894</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>43894</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>43895</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>43898</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>43900</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>43903</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>43903</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>43908</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>43910</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>43915</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>43918</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>43921</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>43921</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>43922</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>43923</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>43923</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43923</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43923</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>43923</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>43923</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>43924</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>43949</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43965</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>43965</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>43969</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>43978</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>43983</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>43983</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>43983</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>43983</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43983</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43993</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43999</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44000</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44000</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44006</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44012</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44020</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>44022</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>44036</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44067</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44069</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>44069</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44070</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44081</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44085</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44085</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44085</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44085</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44089</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44090</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44092</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44092</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44092</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44092</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44092</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44092</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44092</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>44093</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>44097</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>44097</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>44103</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44103</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>44104</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>44113</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44116</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44116</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>44118</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44119</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44119</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44120</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44123</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>44124</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>44127</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44127</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44131</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44154</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44154</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44154</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44154</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>44159</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44165</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44166</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>44168</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44174</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44188</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44188</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44188</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44188</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44188</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44209</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44217</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44218</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44224</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>44237</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44244</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>44244</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>44249</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>44264</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>44274</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44281</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>44286</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44291</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>44292</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>44292</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44299</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>44302</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>44316</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>44316</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>44316</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44316</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44316</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44322</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44322</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44322</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44330</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44333</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44336</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>44336</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>44337</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>44341</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44344</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44344</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>44358</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44362</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>44364</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>44368</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>44369</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>44369</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>44370</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>44370</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44370</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44370</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44376</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>44377</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>44377</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44386</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44386</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>44387</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>44393</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44397</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44404</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44405</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44406</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>44413</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>44431</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44434</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44435</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44435</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44439</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>44439</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>44441</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44447</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44449</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44452</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44453</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>44456</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>44456</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44459</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>44459</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>44460</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44462</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44470</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>44476</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44477</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44477</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44482</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44482</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>44502</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>44503</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44508</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>44516</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44533</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>44536</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44543</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44550</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>44552</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44560</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>44560</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44572</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44579</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44579</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44581</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44590</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>44599</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>44600</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44602</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44603</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44616</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44643</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44652</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44656</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>44658</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>44662</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44680</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>44685</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44687</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>44687</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>44700</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44701</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>44706</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44706</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44708</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44711</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44715</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44720</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44720</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44725</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>44729</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44730</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44730</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44730</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44730</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44731</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44731</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44731</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44731</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44731</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44731</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44731</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44731</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>44730</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44731</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>44731</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>44731</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>44731</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44732</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>44733</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44741</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44743</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44771</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>44771</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>44771</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44785</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44789</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44805</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44805</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44809</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44809</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44811</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>44813</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44817</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>44817</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>44819</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>44820</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>44820</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>44820</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>44825</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>44825</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>44825</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44826</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44826</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44827</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44827</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44827</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>44827</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>44830</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>44831</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44831</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44831</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44832</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44833</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44833</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44841</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44844</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44844</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44844</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44844</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44844</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44845</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>44848</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44851</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44851</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44853</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44854</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44859</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>44859</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44859</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>44859</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>44859</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>44859</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>44859</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44861</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44862</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44865</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>44867</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>44867</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>44869</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44869</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44869</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>44872</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44872</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44872</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>44872</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44874</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>44879</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>44879</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>44879</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>44880</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>44883</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44883</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44886</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44887</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44890</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44890</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44893</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44893</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44893</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44895</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>44903</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44907</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>44907</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44915</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44915</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44915</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44916</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44923</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>44929</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>44929</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44929</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>44937</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44938</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>44939</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>44942</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>44950</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44957</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>44957</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44958</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>44958</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44960</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44960</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44960</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44960</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44960</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44964</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>44965</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44966</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44967</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>44970</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44970</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>44970</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44971</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44972</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44974</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>44978</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>44981</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>44994</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>44994</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>44998</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45002</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45002</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45002</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45013</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45021</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45030</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45034</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45034</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45034</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45034</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45043</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>45043</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>45043</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45044</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45044</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>45044</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45056</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45058</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45058</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45058</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45062</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45062</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45062</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45062</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45063</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45063</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45063</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45063</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45063</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45063</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45063</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45063</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45068</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45068</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45068</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45068</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45068</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45069</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45069</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45070</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45070</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45070</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45070</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45071</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45078</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45079</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45079</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45082</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45082</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45084</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45086</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45086</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>45089</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>45091</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>45093</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45093</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45098</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45098</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45098</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45098</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45099</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45099</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45099</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45099</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45099</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45105</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>45105</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>45106</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45107</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45107</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45110</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45110</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45110</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45110</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45112</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45112</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>45112</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45113</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45113</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45114</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45114</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>45114</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45114</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45117</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45118</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45119</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45119</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45119</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>45121</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45121</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45125</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45125</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45125</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45126</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45127</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45128</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45128</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45128</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>45131</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>45131</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45132</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>45134</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45134</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45134</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45134</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45134</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45135</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45140</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45140</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45142</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>45148</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45149</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45149</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45149</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45152</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45152</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>45152</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45155</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45156</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45156</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45156</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>45156</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45156</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45161</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45161</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45161</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45161</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45161</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45163</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>45163</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>45166</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45166</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45166</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45166</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45167</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45167</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45167</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45167</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45168</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45168</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45168</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45168</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>45168</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45168</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45170</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45170</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45170</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45173</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45174</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45175</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45175</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43654,7 +43654,7 @@
         <v>45175</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45176</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45177</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45177</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45177</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45177</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45177</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45180</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45180</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45182</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>45182</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45182</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45183</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45184</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45184</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45184</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45187</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45187</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45187</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45187</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45187</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>45187</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45188</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45188</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45188</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>45188</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>45188</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45189</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45191</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45191</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45191</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45191</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>45191</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45191</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>45194</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>45195</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45196</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45196</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45198</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45198</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>45198</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45198</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45198</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45198</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45198</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45198</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45198</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45202</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45202</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>45202</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45202</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45204</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45204</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45205</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45205</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>45205</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>45205</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45208</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>45210</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47840,7 +47840,7 @@
         <v>45212</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45212</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45215</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45215</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45216</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45217</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>45218</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>45219</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45219</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45219</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45219</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45223</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45224</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>45225</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45225</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45225</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45225</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45226</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45226</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45226</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45230</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45230</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45230</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45230</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45230</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45236</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>45236</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>45237</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>45239</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>45243</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45243</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45243</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45244</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50002,7 +50002,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45247</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50121,7 +50121,7 @@
         <v>45247</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45247</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45249</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45253</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45253</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45253</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45253</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>45254</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45257</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45257</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45257</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45260</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45265</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45273</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45280</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51254,7 +51254,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51368,7 +51368,7 @@
         <v>45288</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45297</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>45301</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51601,7 +51601,7 @@
         <v>45301</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51658,7 +51658,7 @@
         <v>45302</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45303</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>45307</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45308</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45313</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45313</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45313</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>45313</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45317</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52189,14 +52189,14 @@
     <row r="829" ht="15" customHeight="1">
       <c r="A829" t="inlineStr">
         <is>
-          <t>A 3277-2024</t>
+          <t>A 3349-2024</t>
         </is>
       </c>
       <c r="B829" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         </is>
       </c>
       <c r="G829" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -52246,14 +52246,14 @@
     <row r="830" ht="15" customHeight="1">
       <c r="A830" t="inlineStr">
         <is>
-          <t>A 3687-2024</t>
+          <t>A 3277-2024</t>
         </is>
       </c>
       <c r="B830" s="1" t="n">
-        <v>45321</v>
+        <v>45317</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="G830" t="n">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -52303,14 +52303,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 3809-2024</t>
+          <t>A 3687-2024</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         </is>
       </c>
       <c r="G831" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -52360,14 +52360,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 5576-2024</t>
+          <t>A 3809-2024</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
-        <v>45334</v>
+        <v>45321</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -52417,116 +52417,230 @@
     <row r="833" ht="15" customHeight="1">
       <c r="A833" t="inlineStr">
         <is>
+          <t>A 5576-2024</t>
+        </is>
+      </c>
+      <c r="B833" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="C833" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="G833" t="n">
+        <v>7</v>
+      </c>
+      <c r="H833" t="n">
+        <v>0</v>
+      </c>
+      <c r="I833" t="n">
+        <v>0</v>
+      </c>
+      <c r="J833" t="n">
+        <v>0</v>
+      </c>
+      <c r="K833" t="n">
+        <v>0</v>
+      </c>
+      <c r="L833" t="n">
+        <v>0</v>
+      </c>
+      <c r="M833" t="n">
+        <v>0</v>
+      </c>
+      <c r="N833" t="n">
+        <v>0</v>
+      </c>
+      <c r="O833" t="n">
+        <v>0</v>
+      </c>
+      <c r="P833" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q833" t="n">
+        <v>0</v>
+      </c>
+      <c r="R833" s="2" t="inlineStr"/>
+    </row>
+    <row r="834" ht="15" customHeight="1">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>A 5947-2024</t>
+        </is>
+      </c>
+      <c r="B834" s="1" t="n">
+        <v>45335</v>
+      </c>
+      <c r="C834" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="G834" t="n">
+        <v>5</v>
+      </c>
+      <c r="H834" t="n">
+        <v>0</v>
+      </c>
+      <c r="I834" t="n">
+        <v>0</v>
+      </c>
+      <c r="J834" t="n">
+        <v>0</v>
+      </c>
+      <c r="K834" t="n">
+        <v>0</v>
+      </c>
+      <c r="L834" t="n">
+        <v>0</v>
+      </c>
+      <c r="M834" t="n">
+        <v>0</v>
+      </c>
+      <c r="N834" t="n">
+        <v>0</v>
+      </c>
+      <c r="O834" t="n">
+        <v>0</v>
+      </c>
+      <c r="P834" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q834" t="n">
+        <v>0</v>
+      </c>
+      <c r="R834" s="2" t="inlineStr"/>
+    </row>
+    <row r="835" ht="15" customHeight="1">
+      <c r="A835" t="inlineStr">
+        <is>
           <t>A 5841-2024</t>
         </is>
       </c>
-      <c r="B833" s="1" t="n">
+      <c r="B835" s="1" t="n">
         <v>45335</v>
       </c>
-      <c r="C833" s="1" t="n">
-        <v>45340</v>
-      </c>
-      <c r="D833" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="E833" t="inlineStr">
-        <is>
-          <t>LUDVIKA</t>
-        </is>
-      </c>
-      <c r="G833" t="n">
+      <c r="C835" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="G835" t="n">
         <v>1.6</v>
       </c>
-      <c r="H833" t="n">
-        <v>0</v>
-      </c>
-      <c r="I833" t="n">
-        <v>0</v>
-      </c>
-      <c r="J833" t="n">
-        <v>0</v>
-      </c>
-      <c r="K833" t="n">
-        <v>0</v>
-      </c>
-      <c r="L833" t="n">
-        <v>0</v>
-      </c>
-      <c r="M833" t="n">
-        <v>0</v>
-      </c>
-      <c r="N833" t="n">
-        <v>0</v>
-      </c>
-      <c r="O833" t="n">
-        <v>0</v>
-      </c>
-      <c r="P833" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q833" t="n">
-        <v>0</v>
-      </c>
-      <c r="R833" s="2" t="inlineStr"/>
-    </row>
-    <row r="834">
-      <c r="A834" t="inlineStr">
+      <c r="H835" t="n">
+        <v>0</v>
+      </c>
+      <c r="I835" t="n">
+        <v>0</v>
+      </c>
+      <c r="J835" t="n">
+        <v>0</v>
+      </c>
+      <c r="K835" t="n">
+        <v>0</v>
+      </c>
+      <c r="L835" t="n">
+        <v>0</v>
+      </c>
+      <c r="M835" t="n">
+        <v>0</v>
+      </c>
+      <c r="N835" t="n">
+        <v>0</v>
+      </c>
+      <c r="O835" t="n">
+        <v>0</v>
+      </c>
+      <c r="P835" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q835" t="n">
+        <v>0</v>
+      </c>
+      <c r="R835" s="2" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
         <is>
           <t>A 6151-2024</t>
         </is>
       </c>
-      <c r="B834" s="1" t="n">
+      <c r="B836" s="1" t="n">
         <v>45337</v>
       </c>
-      <c r="C834" s="1" t="n">
-        <v>45340</v>
-      </c>
-      <c r="D834" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="E834" t="inlineStr">
-        <is>
-          <t>LUDVIKA</t>
-        </is>
-      </c>
-      <c r="G834" t="n">
+      <c r="C836" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="G836" t="n">
         <v>1.7</v>
       </c>
-      <c r="H834" t="n">
-        <v>0</v>
-      </c>
-      <c r="I834" t="n">
-        <v>0</v>
-      </c>
-      <c r="J834" t="n">
-        <v>0</v>
-      </c>
-      <c r="K834" t="n">
-        <v>0</v>
-      </c>
-      <c r="L834" t="n">
-        <v>0</v>
-      </c>
-      <c r="M834" t="n">
-        <v>0</v>
-      </c>
-      <c r="N834" t="n">
-        <v>0</v>
-      </c>
-      <c r="O834" t="n">
-        <v>0</v>
-      </c>
-      <c r="P834" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q834" t="n">
-        <v>0</v>
-      </c>
-      <c r="R834" s="2" t="inlineStr"/>
+      <c r="H836" t="n">
+        <v>0</v>
+      </c>
+      <c r="I836" t="n">
+        <v>0</v>
+      </c>
+      <c r="J836" t="n">
+        <v>0</v>
+      </c>
+      <c r="K836" t="n">
+        <v>0</v>
+      </c>
+      <c r="L836" t="n">
+        <v>0</v>
+      </c>
+      <c r="M836" t="n">
+        <v>0</v>
+      </c>
+      <c r="N836" t="n">
+        <v>0</v>
+      </c>
+      <c r="O836" t="n">
+        <v>0</v>
+      </c>
+      <c r="P836" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q836" t="n">
+        <v>0</v>
+      </c>
+      <c r="R836" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -569,7 +569,7 @@
         <v>44322</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>44761</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>45204</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44221</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>44937</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45084</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45162</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>44000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44435</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>45013</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45196</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45239</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>43452</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>43510</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44188</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45099</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>43872</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44322</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44480</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>44831</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>44998</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>45061</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45121</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45211</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>43389</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>43453</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>43581</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>43873</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44167</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44188</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44410</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44456</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44547</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>44560</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44571</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44693</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44694</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>44706</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44825</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44832</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44874</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>44888</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45035</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>45041</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45089</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45093</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45126</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>45140</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>45153</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45189</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45197</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45208</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>43355</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>43363</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>43385</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>43385</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>43389</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>43389</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43403</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>43404</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>43404</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>43404</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>43411</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>43413</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>43416</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>43425</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>43427</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>43436</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>43447</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>43451</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>43452</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>43472</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>43472</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>43472</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>43473</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>43474</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>43494</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>43497</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>43500</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>43501</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>43502</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43531</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>43532</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>43546</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>43551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>43557</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>43566</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>43593</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>43594</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>43601</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>43605</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>43614</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>43628</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43630</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43630</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43633</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>43649</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>43656</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>43662</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>43664</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>43681</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>43705</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>43714</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43720</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>43731</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>43733</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>43734</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43747</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43770</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43780</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43782</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43788</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43791</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>43797</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>43798</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>43798</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>43798</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>43798</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43801</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43817</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43819</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43847</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43847</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43858</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>43860</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43861</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>43861</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>43868</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>43868</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>43872</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>43873</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>43881</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>43881</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>43882</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>43887</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>43887</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>43892</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>43892</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43893</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43893</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43894</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>43894</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>43895</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>43898</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>43900</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>43903</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>43903</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>43908</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>43910</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>43915</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>43918</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>43921</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>43921</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>43922</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>43923</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>43923</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43923</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43923</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>43923</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>43923</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>43924</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>43949</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43965</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>43965</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>43969</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>43978</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>43983</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>43983</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>43983</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>43983</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43983</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43993</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43999</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44000</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44000</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44006</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44012</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44020</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>44022</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>44036</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44067</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44069</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>44069</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44070</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44081</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44085</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44085</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44085</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44085</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44089</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44090</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44092</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44092</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44092</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44092</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44092</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44092</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44092</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>44093</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>44097</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>44097</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>44103</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44103</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>44104</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>44113</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44116</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44116</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>44118</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44119</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44119</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44120</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44123</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>44124</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>44127</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44127</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44131</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44154</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44154</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44154</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44154</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>44159</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44165</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44166</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>44168</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44174</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44188</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44188</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44188</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44188</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44188</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44209</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44217</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44218</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44224</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>44237</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44244</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>44244</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>44249</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>44264</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>44274</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44281</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>44286</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44291</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>44292</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>44292</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44299</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>44302</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>44316</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>44316</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>44316</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44316</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44316</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44322</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44322</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44322</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44330</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44333</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44336</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>44336</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>44337</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>44341</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44344</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44344</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>44358</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44362</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>44364</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>44368</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>44369</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>44369</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>44370</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>44370</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44370</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44370</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44376</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>44377</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>44377</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44386</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44386</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>44387</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>44393</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44397</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44404</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44405</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44406</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>44413</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>44431</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44434</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44435</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44435</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44439</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>44439</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>44441</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44447</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44449</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44452</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44453</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>44456</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>44456</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44459</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>44459</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>44460</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44462</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44470</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>44476</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44477</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44477</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44482</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44482</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>44502</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>44503</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44508</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>44516</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44533</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>44536</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44543</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44550</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>44552</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44560</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>44560</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44572</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44579</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44579</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44581</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44590</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>44599</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>44600</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44602</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44603</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44616</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44643</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44652</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44656</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>44658</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>44662</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44680</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>44685</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44687</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>44687</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>44700</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44701</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>44706</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44706</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44708</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44711</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44715</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44720</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44720</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44725</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>44729</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44730</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44730</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44730</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44730</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44731</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44731</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44731</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44731</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44731</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44731</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44731</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44731</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>44730</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44731</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>44731</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>44731</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>44731</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44732</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>44733</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44741</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44743</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44771</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>44771</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>44771</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44785</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44789</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44805</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44805</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44809</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44809</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44811</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>44813</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44817</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>44817</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>44819</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>44820</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>44820</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>44820</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>44825</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>44825</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>44825</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44826</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44826</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44827</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44827</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44827</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>44827</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>44830</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>44831</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44831</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44831</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44832</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44833</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44833</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44841</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44844</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44844</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44844</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44844</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44844</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44845</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>44848</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44851</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44851</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44853</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44854</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44859</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>44859</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44859</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>44859</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>44859</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>44859</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>44859</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44861</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44862</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44865</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>44867</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>44867</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>44869</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44869</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44869</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>44872</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44872</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44872</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>44872</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44874</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>44879</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>44879</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>44879</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>44880</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>44883</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44883</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44886</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44887</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44890</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44890</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44893</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44893</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44893</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44895</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>44903</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44907</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>44907</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44915</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44915</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44915</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44916</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44923</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>44929</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>44929</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44929</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>44937</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44938</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>44939</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>44942</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>44950</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44957</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>44957</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44958</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>44958</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44960</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44960</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44960</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44960</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44960</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44964</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>44965</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44966</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44967</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>44970</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44970</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>44970</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44971</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44972</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44974</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>44978</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>44981</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>44994</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>44994</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>44998</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45002</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45002</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45002</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45013</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45021</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45030</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45034</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45034</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45034</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45034</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45043</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>45043</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>45043</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45044</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45044</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>45044</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45056</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45058</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45058</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45058</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45062</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45062</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45062</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45062</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45063</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45063</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45063</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45063</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45063</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45063</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45063</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45063</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45068</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45068</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45068</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45068</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45068</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45069</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45069</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45070</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45070</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45070</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45070</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45071</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45078</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45079</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45079</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45082</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45082</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45084</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45086</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45086</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>45089</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>45091</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>45093</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45093</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45098</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45098</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45098</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45098</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45099</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45099</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45099</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45099</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45099</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45105</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>45105</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>45106</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45107</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45107</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45110</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45110</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45110</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45110</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45112</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45112</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>45112</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45113</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45113</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45114</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45114</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>45114</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45114</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45117</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45118</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45119</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45119</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45119</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>45121</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45121</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45125</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45125</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45125</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45126</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45127</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45128</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45128</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45128</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>45131</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>45131</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45132</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>45134</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45134</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45134</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45134</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45134</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45135</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45140</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45140</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45142</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>45148</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45149</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45149</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45149</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45152</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45152</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>45152</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45155</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45156</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45156</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45156</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>45156</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45156</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45161</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45161</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45161</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45161</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45161</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45163</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>45163</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>45166</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45166</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45166</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45166</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45167</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45167</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45167</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45167</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45168</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45168</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45168</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45168</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>45168</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45168</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45170</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45170</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45170</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45173</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45174</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45175</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45175</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43654,7 +43654,7 @@
         <v>45175</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45176</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45177</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45177</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45177</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45177</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45177</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45180</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45180</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45182</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>45182</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45182</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45183</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45184</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45184</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45184</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45187</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45187</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45187</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45187</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45187</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>45187</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45188</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45188</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45188</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>45188</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>45188</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45189</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45191</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45191</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45191</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45191</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>45191</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45191</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>45194</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>45195</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45196</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45196</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45198</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45198</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>45198</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45198</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45198</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45198</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45198</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45198</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45198</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45202</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45202</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>45202</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45202</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45204</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45204</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45205</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45205</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>45205</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>45205</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45208</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>45210</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47840,7 +47840,7 @@
         <v>45212</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45212</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45215</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45215</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45216</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45217</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>45218</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>45219</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45219</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45219</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45219</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45223</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45224</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>45225</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45225</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45225</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45225</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45226</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45226</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45226</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45230</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45230</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45230</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45230</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45230</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45236</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>45236</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>45237</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>45239</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>45243</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45243</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45243</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45244</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50002,7 +50002,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45247</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50121,7 +50121,7 @@
         <v>45247</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45247</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45249</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45253</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45253</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45253</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45253</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>45254</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45257</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45257</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45257</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45260</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45265</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45273</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45280</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51254,7 +51254,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51368,7 +51368,7 @@
         <v>45288</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45297</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>45301</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51601,7 +51601,7 @@
         <v>45301</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51658,7 +51658,7 @@
         <v>45302</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45303</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>45307</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45308</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51884,14 +51884,14 @@
     <row r="824" ht="15" customHeight="1">
       <c r="A824" t="inlineStr">
         <is>
-          <t>A 2481-2024</t>
+          <t>A 2484-2024</t>
         </is>
       </c>
       <c r="B824" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51904,128 +51904,128 @@
         </is>
       </c>
       <c r="G824" t="n">
+        <v>1</v>
+      </c>
+      <c r="H824" t="n">
+        <v>0</v>
+      </c>
+      <c r="I824" t="n">
+        <v>0</v>
+      </c>
+      <c r="J824" t="n">
+        <v>0</v>
+      </c>
+      <c r="K824" t="n">
+        <v>0</v>
+      </c>
+      <c r="L824" t="n">
+        <v>0</v>
+      </c>
+      <c r="M824" t="n">
+        <v>0</v>
+      </c>
+      <c r="N824" t="n">
+        <v>0</v>
+      </c>
+      <c r="O824" t="n">
+        <v>0</v>
+      </c>
+      <c r="P824" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q824" t="n">
+        <v>0</v>
+      </c>
+      <c r="R824" s="2" t="inlineStr"/>
+    </row>
+    <row r="825" ht="15" customHeight="1">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>A 2481-2024</t>
+        </is>
+      </c>
+      <c r="B825" s="1" t="n">
+        <v>45313</v>
+      </c>
+      <c r="C825" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="G825" t="n">
         <v>4.8</v>
       </c>
-      <c r="H824" t="n">
-        <v>0</v>
-      </c>
-      <c r="I824" t="n">
-        <v>0</v>
-      </c>
-      <c r="J824" t="n">
-        <v>0</v>
-      </c>
-      <c r="K824" t="n">
-        <v>0</v>
-      </c>
-      <c r="L824" t="n">
-        <v>0</v>
-      </c>
-      <c r="M824" t="n">
-        <v>0</v>
-      </c>
-      <c r="N824" t="n">
-        <v>0</v>
-      </c>
-      <c r="O824" t="n">
-        <v>0</v>
-      </c>
-      <c r="P824" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q824" t="n">
-        <v>0</v>
-      </c>
-      <c r="R824" s="2" t="inlineStr"/>
-      <c r="U824">
+      <c r="H825" t="n">
+        <v>0</v>
+      </c>
+      <c r="I825" t="n">
+        <v>0</v>
+      </c>
+      <c r="J825" t="n">
+        <v>0</v>
+      </c>
+      <c r="K825" t="n">
+        <v>0</v>
+      </c>
+      <c r="L825" t="n">
+        <v>0</v>
+      </c>
+      <c r="M825" t="n">
+        <v>0</v>
+      </c>
+      <c r="N825" t="n">
+        <v>0</v>
+      </c>
+      <c r="O825" t="n">
+        <v>0</v>
+      </c>
+      <c r="P825" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q825" t="n">
+        <v>0</v>
+      </c>
+      <c r="R825" s="2" t="inlineStr"/>
+      <c r="U825">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/knärot/A 2481-2024 karta knärot.png", "A 2481-2024")</f>
         <v/>
       </c>
-      <c r="V824">
+      <c r="V825">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomål/A 2481-2024 FSC-klagomål.docx", "A 2481-2024")</f>
         <v/>
       </c>
-      <c r="W824">
+      <c r="W825">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomålsmail/A 2481-2024 FSC-klagomål mail.docx", "A 2481-2024")</f>
         <v/>
       </c>
-      <c r="X824">
+      <c r="X825">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsyn/A 2481-2024 tillsynsbegäran.docx", "A 2481-2024")</f>
         <v/>
       </c>
-      <c r="Y824">
+      <c r="Y825">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsynsmail/A 2481-2024 tillsynsbegäran mail.docx", "A 2481-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="825" ht="15" customHeight="1">
-      <c r="A825" t="inlineStr">
-        <is>
-          <t>A 2485-2024</t>
-        </is>
-      </c>
-      <c r="B825" s="1" t="n">
-        <v>45313</v>
-      </c>
-      <c r="C825" s="1" t="n">
-        <v>45343</v>
-      </c>
-      <c r="D825" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="E825" t="inlineStr">
-        <is>
-          <t>LUDVIKA</t>
-        </is>
-      </c>
-      <c r="G825" t="n">
-        <v>2</v>
-      </c>
-      <c r="H825" t="n">
-        <v>0</v>
-      </c>
-      <c r="I825" t="n">
-        <v>0</v>
-      </c>
-      <c r="J825" t="n">
-        <v>0</v>
-      </c>
-      <c r="K825" t="n">
-        <v>0</v>
-      </c>
-      <c r="L825" t="n">
-        <v>0</v>
-      </c>
-      <c r="M825" t="n">
-        <v>0</v>
-      </c>
-      <c r="N825" t="n">
-        <v>0</v>
-      </c>
-      <c r="O825" t="n">
-        <v>0</v>
-      </c>
-      <c r="P825" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q825" t="n">
-        <v>0</v>
-      </c>
-      <c r="R825" s="2" t="inlineStr"/>
-    </row>
     <row r="826" ht="15" customHeight="1">
       <c r="A826" t="inlineStr">
         <is>
-          <t>A 2484-2024</t>
+          <t>A 2485-2024</t>
         </is>
       </c>
       <c r="B826" s="1" t="n">
         <v>45313</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         </is>
       </c>
       <c r="G826" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H826" t="n">
         <v>0</v>
@@ -52082,7 +52082,7 @@
         <v>45313</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45317</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52189,14 +52189,14 @@
     <row r="829" ht="15" customHeight="1">
       <c r="A829" t="inlineStr">
         <is>
-          <t>A 3349-2024</t>
+          <t>A 3277-2024</t>
         </is>
       </c>
       <c r="B829" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         </is>
       </c>
       <c r="G829" t="n">
-        <v>3.8</v>
+        <v>0.3</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -52246,14 +52246,14 @@
     <row r="830" ht="15" customHeight="1">
       <c r="A830" t="inlineStr">
         <is>
-          <t>A 3277-2024</t>
+          <t>A 3349-2024</t>
         </is>
       </c>
       <c r="B830" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="G830" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -52310,7 +52310,7 @@
         <v>45321</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52367,7 +52367,7 @@
         <v>45321</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         <v>45334</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52474,14 +52474,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 5947-2024</t>
+          <t>A 5841-2024</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         </is>
       </c>
       <c r="G834" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -52531,14 +52531,14 @@
     <row r="835" ht="15" customHeight="1">
       <c r="A835" t="inlineStr">
         <is>
-          <t>A 5841-2024</t>
+          <t>A 5947-2024</t>
         </is>
       </c>
       <c r="B835" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         </is>
       </c>
       <c r="G835" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -52595,7 +52595,7 @@
         <v>45337</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -569,7 +569,7 @@
         <v>44322</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>44761</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>45204</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44221</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>44937</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45084</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45162</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>44000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44435</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>45013</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45196</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45239</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>43452</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>43510</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44188</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45099</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>43872</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44322</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44480</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>44831</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>44998</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>45061</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45121</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45211</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>43389</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>43453</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>43581</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>43873</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44167</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44188</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44410</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44456</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44547</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>44560</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44571</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44693</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44694</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>44706</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44825</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44832</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44874</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>44888</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45035</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>45041</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45089</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45093</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45126</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>45140</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>45153</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45189</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45197</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45208</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>43355</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>43363</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>43385</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>43385</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>43389</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>43389</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43403</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>43404</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>43404</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>43404</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>43411</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>43413</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>43416</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>43425</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>43427</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>43436</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>43447</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>43451</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>43452</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>43472</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>43472</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>43472</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>43473</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>43474</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>43494</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>43497</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>43500</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>43501</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>43502</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43531</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>43532</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>43546</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>43551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>43557</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>43566</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>43593</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>43594</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>43601</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>43605</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>43614</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>43628</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43630</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43630</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43633</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>43649</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>43656</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>43662</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>43664</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>43681</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>43705</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>43714</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43720</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>43731</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>43733</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>43734</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43747</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43770</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43780</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43782</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43788</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43791</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>43797</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>43798</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>43798</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>43798</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>43798</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43801</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43817</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43819</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43847</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43847</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43858</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>43860</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43861</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>43861</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>43868</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>43868</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>43872</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>43873</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>43881</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>43881</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>43882</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>43887</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>43887</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>43892</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>43892</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43893</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43893</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43894</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>43894</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>43895</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>43898</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>43900</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>43903</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>43903</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>43908</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>43910</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>43915</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>43918</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>43921</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>43921</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>43922</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>43923</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>43923</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43923</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43923</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>43923</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>43923</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>43924</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>43949</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43965</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>43965</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>43969</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>43978</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>43983</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>43983</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>43983</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>43983</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43983</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43993</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43999</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44000</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44000</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44006</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44012</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44020</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>44022</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>44036</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44067</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44069</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>44069</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44070</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44081</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44085</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44085</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44085</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44085</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44089</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44090</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44092</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44092</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44092</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44092</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44092</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44092</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44092</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>44093</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>44097</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>44097</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>44103</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44103</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>44104</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>44113</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44116</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44116</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>44118</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44119</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44119</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44120</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44123</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>44124</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>44127</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44127</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44131</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44154</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44154</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44154</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44154</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>44159</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44165</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44166</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>44168</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44174</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44188</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44188</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44188</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44188</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44188</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44209</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44217</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44218</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44224</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>44237</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44244</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>44244</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>44249</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>44264</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>44274</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44281</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>44286</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44291</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>44292</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>44292</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44299</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>44302</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>44316</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>44316</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>44316</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44316</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44316</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44322</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44322</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44322</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44330</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44333</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44336</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>44336</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>44337</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>44341</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44344</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44344</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>44358</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44362</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>44364</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>44368</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>44369</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>44369</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>44370</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>44370</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44370</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44370</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44376</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>44377</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>44377</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44386</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44386</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>44387</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>44393</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44397</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44404</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44405</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44406</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>44413</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>44431</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44434</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44435</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44435</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44439</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>44439</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>44441</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44447</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44449</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44452</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44453</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>44456</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>44456</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44459</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>44459</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>44460</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44462</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44470</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>44476</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44477</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44477</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44482</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44482</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>44502</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>44503</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44508</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>44516</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44533</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>44536</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44543</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44550</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>44552</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44560</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>44560</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44572</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44579</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44579</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44581</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44590</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>44599</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>44600</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44602</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44603</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44616</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44643</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44652</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44656</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>44658</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>44662</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44680</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>44685</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44687</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>44687</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>44700</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44701</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>44706</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44706</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44708</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44711</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44715</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44720</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44720</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44725</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>44729</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44730</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44730</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44730</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44730</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44731</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44731</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44731</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44731</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44731</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44731</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44731</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44731</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>44730</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44731</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>44731</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>44731</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>44731</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44732</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>44733</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44741</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44743</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44771</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>44771</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>44771</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44785</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44789</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44805</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44805</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44809</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44809</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44811</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>44813</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44817</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>44817</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>44819</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>44820</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>44820</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>44820</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>44825</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>44825</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>44825</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44826</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44826</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44827</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44827</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44827</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>44827</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>44830</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>44831</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44831</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44831</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44832</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44833</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44833</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44841</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44844</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44844</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44844</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44844</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44844</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44845</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>44848</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44851</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44851</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44853</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44854</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44859</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>44859</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44859</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>44859</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>44859</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>44859</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>44859</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44861</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44862</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44865</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>44867</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>44867</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>44869</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44869</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44869</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>44872</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44872</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44872</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>44872</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44874</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>44879</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>44879</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>44879</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>44880</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>44883</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44883</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44886</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44887</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44890</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44890</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44893</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44893</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44893</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44895</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>44903</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44907</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>44907</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44915</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44915</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44915</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44916</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44923</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>44929</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>44929</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44929</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>44937</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44938</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>44939</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>44942</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>44950</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44957</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>44957</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44958</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>44958</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44960</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44960</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44960</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44960</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44960</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44964</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>44965</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44966</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44967</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>44970</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44970</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>44970</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44971</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44972</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44974</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>44978</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>44981</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>44994</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>44994</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>44998</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45002</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45002</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45002</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45013</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45021</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45030</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45034</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45034</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45034</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45034</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45043</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>45043</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>45043</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45044</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45044</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>45044</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45056</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45058</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45058</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45058</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45062</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45062</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45062</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45062</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45063</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45063</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45063</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45063</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45063</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45063</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45063</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45063</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45068</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45068</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45068</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45068</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45068</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45069</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45069</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45070</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45070</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45070</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45070</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45071</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45078</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45079</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45079</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45082</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45082</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45084</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45086</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45086</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>45089</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>45091</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>45093</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45093</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45098</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45098</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45098</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45098</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45099</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45099</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45099</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45099</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45099</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45105</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>45105</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>45106</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45107</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45107</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45110</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45110</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45110</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45110</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45112</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45112</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>45112</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45113</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45113</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45114</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45114</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>45114</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45114</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45117</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45118</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45119</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45119</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45119</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>45121</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45121</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45125</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45125</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45125</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45126</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45127</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45128</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45128</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45128</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>45131</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>45131</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45132</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>45134</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45134</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45134</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45134</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45134</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45135</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45140</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45140</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45142</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>45148</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45149</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45149</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45149</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45152</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45152</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>45152</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45155</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45156</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45156</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45156</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>45156</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45156</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45161</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45161</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45161</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45161</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45161</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45163</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>45163</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>45166</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45166</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45166</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45166</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45167</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45167</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45167</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45167</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45168</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45168</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45168</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45168</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>45168</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45168</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45170</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45170</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45170</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45173</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45174</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45175</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45175</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43654,7 +43654,7 @@
         <v>45175</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45176</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45177</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45177</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45177</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45177</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45177</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45180</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45180</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45182</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>45182</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45182</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45183</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45184</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45184</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45184</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45187</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45187</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45187</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45187</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45187</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>45187</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45188</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45188</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45188</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>45188</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>45188</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45189</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45191</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45191</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45191</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45191</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>45191</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45191</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>45194</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>45195</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45196</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45196</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45198</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45198</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>45198</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45198</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45198</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45198</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45198</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45198</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45198</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45202</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45202</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>45202</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45202</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45204</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45204</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45205</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45205</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>45205</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>45205</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45208</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>45210</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47840,7 +47840,7 @@
         <v>45212</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45212</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45215</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45215</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45216</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45217</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>45218</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>45219</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45219</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45219</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45219</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45223</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45224</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>45225</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45225</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45225</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45225</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45226</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45226</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45226</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45230</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45230</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45230</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45230</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45230</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45236</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>45236</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>45237</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>45239</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>45243</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45243</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45243</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45244</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50002,7 +50002,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45247</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50121,7 +50121,7 @@
         <v>45247</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45247</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45249</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45253</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45253</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45253</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45253</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>45254</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45257</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45257</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45257</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45260</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45265</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45273</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45280</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51254,7 +51254,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51368,7 +51368,7 @@
         <v>45288</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45297</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>45301</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51601,7 +51601,7 @@
         <v>45301</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51658,7 +51658,7 @@
         <v>45302</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45303</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>45307</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45308</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45313</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51948,7 +51948,7 @@
         <v>45313</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45313</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>45313</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52132,14 +52132,14 @@
     <row r="828" ht="15" customHeight="1">
       <c r="A828" t="inlineStr">
         <is>
-          <t>A 3280-2024</t>
+          <t>A 3277-2024</t>
         </is>
       </c>
       <c r="B828" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         </is>
       </c>
       <c r="G828" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H828" t="n">
         <v>0</v>
@@ -52189,14 +52189,14 @@
     <row r="829" ht="15" customHeight="1">
       <c r="A829" t="inlineStr">
         <is>
-          <t>A 3277-2024</t>
+          <t>A 3280-2024</t>
         </is>
       </c>
       <c r="B829" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         </is>
       </c>
       <c r="G829" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H829" t="n">
         <v>0</v>
@@ -52253,7 +52253,7 @@
         <v>45317</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52310,7 +52310,7 @@
         <v>45321</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52367,7 +52367,7 @@
         <v>45321</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         <v>45334</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52474,14 +52474,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 5841-2024</t>
+          <t>A 5947-2024</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         </is>
       </c>
       <c r="G834" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -52531,14 +52531,14 @@
     <row r="835" ht="15" customHeight="1">
       <c r="A835" t="inlineStr">
         <is>
-          <t>A 5947-2024</t>
+          <t>A 5841-2024</t>
         </is>
       </c>
       <c r="B835" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         </is>
       </c>
       <c r="G835" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -52595,7 +52595,7 @@
         <v>45337</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z836"/>
+  <dimension ref="A1:Z837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44322</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>44761</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>45204</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44221</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>44937</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45084</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45162</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>44000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44435</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>45013</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45196</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45239</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>43452</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>43510</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44188</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45099</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>43872</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44322</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44480</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>44831</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>44998</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>45061</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45121</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45211</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>43389</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>43453</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>43581</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>43873</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44167</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44188</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44410</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44456</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44547</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>44560</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44571</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44693</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44694</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>44706</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44825</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44832</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44874</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>44888</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45035</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>45041</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45089</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45093</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45126</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>45140</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>45153</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45189</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45197</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45208</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>43355</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>43363</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>43385</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>43385</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>43389</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>43389</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43403</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>43404</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>43404</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>43404</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>43411</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>43413</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>43416</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>43425</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>43427</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>43436</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>43447</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>43451</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>43452</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>43472</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>43472</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>43472</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>43473</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>43474</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>43494</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>43497</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>43500</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>43501</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>43502</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43531</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>43532</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>43546</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>43551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>43557</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>43566</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>43593</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>43594</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>43601</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>43605</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>43614</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>43628</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43630</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43630</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43633</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>43649</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>43656</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>43662</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>43664</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>43681</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>43705</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>43714</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43720</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>43731</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>43733</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>43734</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43747</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43770</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43780</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43782</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43788</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43791</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>43797</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>43798</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>43798</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>43798</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>43798</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43801</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43817</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43819</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43847</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43847</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43858</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>43860</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43861</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>43861</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>43868</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>43868</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>43872</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>43873</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>43881</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>43881</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>43882</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>43887</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>43887</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>43892</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>43892</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43893</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43893</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43894</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>43894</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>43895</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>43898</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>43900</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>43903</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>43903</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>43908</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>43910</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>43915</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>43918</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>43921</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>43921</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>43922</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>43923</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>43923</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43923</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43923</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>43923</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>43923</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>43924</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>43949</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43965</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>43965</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>43969</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>43978</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>43983</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>43983</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>43983</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>43983</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43983</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43993</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43999</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44000</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44000</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44006</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44012</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44020</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>44022</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>44036</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44067</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44069</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>44069</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44070</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44081</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44085</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44085</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44085</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44085</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44089</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44090</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44092</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44092</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44092</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44092</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44092</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44092</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44092</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>44093</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>44097</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>44097</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>44103</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44103</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>44104</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>44113</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44116</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44116</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>44118</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44119</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44119</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44120</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44123</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>44124</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>44127</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44127</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44131</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44154</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44154</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44154</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44154</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>44159</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44165</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44166</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>44168</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44174</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44188</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44188</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44188</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44188</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44188</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44209</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44217</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44218</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44224</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>44237</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44244</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>44244</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>44249</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>44264</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>44274</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44281</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>44286</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44291</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>44292</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>44292</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44299</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>44302</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>44316</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>44316</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>44316</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44316</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44316</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44322</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44322</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44322</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44330</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44333</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44336</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>44336</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>44337</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>44341</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44344</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44344</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>44358</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44362</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>44364</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>44368</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>44369</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>44369</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>44370</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>44370</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44370</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44370</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44376</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>44377</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>44377</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44386</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44386</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>44387</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>44393</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44397</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44404</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44405</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44406</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>44413</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>44431</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44434</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44435</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44435</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44439</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>44439</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>44441</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44447</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44449</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44452</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44453</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>44456</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>44456</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44459</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>44459</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>44460</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44462</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44470</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>44476</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44477</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44477</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44482</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44482</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>44502</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>44503</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44508</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>44516</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44533</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>44536</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44543</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44550</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>44552</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44560</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>44560</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44572</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44579</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44579</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44581</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44590</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>44599</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>44600</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44602</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44603</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44616</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44643</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44652</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44656</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>44658</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>44662</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44680</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>44685</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44687</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>44687</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>44700</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44701</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>44706</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44706</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44708</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44711</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44715</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44720</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44720</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44725</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>44729</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44730</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44730</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44730</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44730</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44731</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44731</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44731</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44731</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44731</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44731</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44731</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44731</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>44730</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44731</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>44731</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>44731</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>44731</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44732</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>44733</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44741</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44743</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44771</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>44771</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>44771</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44785</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44789</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44805</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44805</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44809</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44809</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44811</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>44813</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44817</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>44817</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>44819</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>44820</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>44820</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>44820</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>44825</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>44825</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>44825</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44826</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44826</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44827</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44827</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44827</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>44827</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>44830</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>44831</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44831</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44831</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44832</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44833</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44833</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44841</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44844</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44844</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44844</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44844</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44844</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44845</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>44848</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44851</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44851</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44853</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44854</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44859</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>44859</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44859</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>44859</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>44859</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>44859</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>44859</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44861</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44862</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44865</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>44867</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>44867</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>44869</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44869</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44869</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>44872</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44872</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44872</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>44872</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44874</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>44879</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>44879</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>44879</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>44880</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>44883</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44883</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44886</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44887</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44890</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44890</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44893</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44893</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44893</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44895</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>44903</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44907</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>44907</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44915</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44915</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44915</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44916</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44923</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>44929</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>44929</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44929</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>44937</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44938</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>44939</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>44942</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>44950</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44957</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>44957</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44958</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>44958</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44960</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44960</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44960</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44960</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44960</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44964</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>44965</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44966</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44967</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>44970</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44970</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>44970</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44971</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44972</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44974</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>44978</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>44981</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>44994</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>44994</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>44998</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45002</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45002</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45002</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45013</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45021</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45030</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45034</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45034</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45034</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45034</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45043</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>45043</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>45043</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45044</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45044</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>45044</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45056</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45058</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45058</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45058</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45062</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45062</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45062</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45062</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45063</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45063</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45063</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45063</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45063</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45063</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45063</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45063</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45068</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45068</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45068</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45068</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45068</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45069</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45069</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45070</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45070</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45070</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45070</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45071</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45078</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45079</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45079</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45082</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45082</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45084</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45086</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45086</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>45089</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>45091</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>45093</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45093</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45098</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45098</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45098</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45098</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45099</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45099</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45099</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45099</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45099</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45105</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>45105</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>45106</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45107</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45107</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45110</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45110</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45110</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45110</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45112</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45112</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>45112</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45113</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45113</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45114</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45114</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>45114</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45114</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45117</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45118</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45119</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45119</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45119</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>45121</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45121</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45125</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45125</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45125</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45126</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45127</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45128</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45128</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45128</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>45131</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>45131</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45132</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>45134</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45134</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45134</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45134</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45134</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45135</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45140</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45140</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45142</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>45148</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45149</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45149</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45149</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45152</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45152</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>45152</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45155</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45156</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45156</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45156</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>45156</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45156</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45161</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45161</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45161</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45161</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45161</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45163</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>45163</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>45166</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45166</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45166</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45166</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45167</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45167</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45167</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45167</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45168</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45168</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45168</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45168</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>45168</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45168</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45170</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45170</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45170</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45173</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45174</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45175</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45175</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43654,7 +43654,7 @@
         <v>45175</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45176</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45177</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45177</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45177</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45177</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45177</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45180</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45180</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45182</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>45182</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45182</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45183</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45184</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45184</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45184</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45187</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45187</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45187</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45187</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45187</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>45187</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45188</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45188</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45188</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>45188</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>45188</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45189</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45191</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45191</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45191</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45191</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>45191</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45191</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>45194</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>45195</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45196</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45196</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45198</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45198</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>45198</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45198</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45198</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45198</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45198</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45198</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45198</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45202</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45202</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>45202</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45202</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45204</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45204</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45205</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45205</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>45205</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>45205</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45208</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>45210</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47840,7 +47840,7 @@
         <v>45212</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45212</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45215</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45215</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45216</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45217</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>45218</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>45219</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45219</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45219</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45219</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45223</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45224</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>45225</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45225</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45225</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45225</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45226</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45226</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45226</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45230</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45230</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45230</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45230</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45230</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45236</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>45236</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>45237</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>45239</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>45243</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45243</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45243</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45244</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50002,7 +50002,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45247</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50121,7 +50121,7 @@
         <v>45247</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45247</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45249</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45253</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45253</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45253</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45253</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>45254</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45257</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45257</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45257</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45260</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45265</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45273</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45280</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51254,7 +51254,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51368,7 +51368,7 @@
         <v>45288</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45297</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>45301</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51601,7 +51601,7 @@
         <v>45301</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51658,7 +51658,7 @@
         <v>45302</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45303</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>45307</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45308</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45313</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51948,7 +51948,7 @@
         <v>45313</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45313</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>45313</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45317</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>45317</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52253,7 +52253,7 @@
         <v>45317</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52310,7 +52310,7 @@
         <v>45321</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52367,7 +52367,7 @@
         <v>45321</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         <v>45334</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52474,14 +52474,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 5947-2024</t>
+          <t>A 5841-2024</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52494,7 +52494,7 @@
         </is>
       </c>
       <c r="G834" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -52531,14 +52531,14 @@
     <row r="835" ht="15" customHeight="1">
       <c r="A835" t="inlineStr">
         <is>
-          <t>A 5841-2024</t>
+          <t>A 5947-2024</t>
         </is>
       </c>
       <c r="B835" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         </is>
       </c>
       <c r="G835" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -52585,7 +52585,7 @@
       </c>
       <c r="R835" s="2" t="inlineStr"/>
     </row>
-    <row r="836">
+    <row r="836" ht="15" customHeight="1">
       <c r="A836" t="inlineStr">
         <is>
           <t>A 6151-2024</t>
@@ -52595,7 +52595,7 @@
         <v>45337</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52641,6 +52641,63 @@
         <v>0</v>
       </c>
       <c r="R836" s="2" t="inlineStr"/>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>A 7317-2024</t>
+        </is>
+      </c>
+      <c r="B837" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C837" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="G837" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H837" t="n">
+        <v>0</v>
+      </c>
+      <c r="I837" t="n">
+        <v>0</v>
+      </c>
+      <c r="J837" t="n">
+        <v>0</v>
+      </c>
+      <c r="K837" t="n">
+        <v>0</v>
+      </c>
+      <c r="L837" t="n">
+        <v>0</v>
+      </c>
+      <c r="M837" t="n">
+        <v>0</v>
+      </c>
+      <c r="N837" t="n">
+        <v>0</v>
+      </c>
+      <c r="O837" t="n">
+        <v>0</v>
+      </c>
+      <c r="P837" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q837" t="n">
+        <v>0</v>
+      </c>
+      <c r="R837" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -569,7 +569,7 @@
         <v>44322</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>44761</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>45204</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44221</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>44937</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45084</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45162</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>44000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44435</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>45013</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45196</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45239</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>43452</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>43510</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44188</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45099</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>43872</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44322</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44480</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>44831</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>44998</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>45061</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45121</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45211</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>43389</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>43453</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>43581</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>43873</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44167</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44188</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44410</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44456</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44547</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>44560</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44571</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44693</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44694</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>44706</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44825</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44832</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44874</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>44888</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45035</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>45041</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45089</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45093</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45126</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>45140</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>45153</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45189</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45197</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45208</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>43355</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>43363</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>43385</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>43385</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>43389</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>43389</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43403</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>43404</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>43404</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>43404</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>43411</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>43413</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>43416</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>43425</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>43427</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>43436</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>43447</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>43451</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>43452</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>43472</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>43472</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>43472</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>43473</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>43474</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>43494</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>43497</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>43500</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>43501</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>43502</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43531</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>43532</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>43546</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>43551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>43557</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>43566</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>43593</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>43594</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>43601</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>43605</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>43614</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>43628</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43630</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43630</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43633</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>43649</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>43656</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>43662</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>43664</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>43681</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>43705</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>43714</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43720</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>43731</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>43733</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>43734</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43747</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43770</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43780</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43782</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43788</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43791</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>43797</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>43798</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>43798</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>43798</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>43798</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43801</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43817</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43819</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43847</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43847</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43858</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>43860</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43861</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>43861</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>43868</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>43868</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>43872</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>43873</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>43881</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>43881</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>43882</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>43887</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>43887</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>43892</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>43892</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43893</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43893</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43894</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>43894</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>43895</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>43898</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>43900</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>43903</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>43903</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>43908</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>43910</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>43915</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>43918</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>43921</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>43921</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>43922</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>43923</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>43923</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43923</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43923</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>43923</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>43923</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>43924</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>43949</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43965</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>43965</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>43969</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>43978</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>43983</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>43983</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>43983</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>43983</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43983</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43993</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43999</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44000</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44000</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44006</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44012</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44020</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>44022</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>44036</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44067</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44069</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>44069</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44070</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44081</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44085</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44085</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44085</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44085</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44089</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44090</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44092</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44092</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44092</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44092</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44092</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44092</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44092</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>44093</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>44097</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>44097</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>44103</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44103</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>44104</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>44113</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44116</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44116</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>44118</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44119</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44119</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44120</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44123</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>44124</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>44127</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44127</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44131</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44154</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44154</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44154</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44154</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>44159</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44165</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44166</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>44168</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44174</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44188</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44188</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44188</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44188</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44188</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44209</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44217</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44218</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44224</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>44237</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44244</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>44244</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>44249</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>44264</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>44274</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44281</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>44286</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44291</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>44292</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>44292</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44299</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>44302</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>44316</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>44316</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>44316</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44316</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44316</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44322</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44322</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44322</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44330</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44333</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44336</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>44336</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>44337</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>44341</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44344</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44344</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>44358</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44362</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>44364</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>44368</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>44369</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>44369</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>44370</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>44370</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44370</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44370</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44376</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>44377</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>44377</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44386</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44386</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>44387</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>44393</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44397</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44404</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44405</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44406</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>44413</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>44431</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44434</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44435</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44435</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44439</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>44439</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>44441</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44447</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44449</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44452</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44453</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>44456</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>44456</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44459</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>44459</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>44460</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44462</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44470</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>44476</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44477</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44477</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44482</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44482</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>44502</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>44503</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44508</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>44516</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44533</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>44536</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44543</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44550</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>44552</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44560</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>44560</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44572</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44579</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44579</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44581</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44590</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>44599</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>44600</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44602</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44603</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44616</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44643</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44652</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44656</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>44658</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>44662</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44680</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>44685</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44687</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>44687</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>44700</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44701</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>44706</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44706</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44708</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44711</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44715</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44720</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44720</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44725</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>44729</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44730</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44730</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44730</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44730</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44731</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44731</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44731</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44731</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44731</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44731</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44731</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44731</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>44730</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44731</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>44731</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>44731</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>44731</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44732</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>44733</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44741</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44743</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44771</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>44771</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>44771</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44785</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44789</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44805</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44805</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44809</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44809</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44811</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>44813</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44817</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>44817</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>44819</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>44820</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>44820</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>44820</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>44825</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>44825</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>44825</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44826</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44826</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44827</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44827</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44827</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>44827</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>44830</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>44831</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44831</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44831</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44832</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44833</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44833</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44841</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44844</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44844</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44844</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44844</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44844</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44845</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>44848</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44851</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44851</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44853</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44854</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44859</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>44859</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44859</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>44859</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>44859</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>44859</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>44859</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44861</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44862</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44865</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>44867</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>44867</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>44869</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44869</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44869</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>44872</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44872</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44872</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>44872</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44874</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>44879</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>44879</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>44879</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>44880</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>44883</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44883</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44886</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44887</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44890</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44890</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44893</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44893</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44893</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44895</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>44903</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44907</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>44907</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44915</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44915</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44915</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44916</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44923</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>44929</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>44929</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44929</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>44937</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44938</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>44939</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>44942</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>44950</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44957</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>44957</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44958</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>44958</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44960</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44960</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44960</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44960</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44960</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44964</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>44965</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44966</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44967</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>44970</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44970</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>44970</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44971</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44972</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44974</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>44978</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>44981</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>44994</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>44994</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>44998</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45002</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45002</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45002</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45013</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45021</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45030</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45034</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45034</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45034</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45034</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45043</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>45043</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>45043</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45044</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45044</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>45044</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45056</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45058</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45058</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45058</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45062</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45062</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45062</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45062</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45063</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45063</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45063</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45063</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45063</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45063</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45063</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45063</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45068</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45068</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45068</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45068</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45068</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45069</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45069</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45070</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45070</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45070</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45070</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45071</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45078</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45079</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45079</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45082</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45082</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45084</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45086</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45086</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>45089</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>45091</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>45093</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45093</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45098</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45098</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45098</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45098</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45099</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45099</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45099</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45099</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45099</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45105</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>45105</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>45106</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45107</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45107</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45110</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45110</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45110</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45110</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45112</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45112</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>45112</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45113</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45113</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45114</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45114</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>45114</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45114</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45117</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45118</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45119</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45119</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45119</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>45121</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45121</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45125</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45125</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45125</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45126</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45127</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45128</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45128</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45128</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>45131</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>45131</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45132</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>45134</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45134</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45134</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45134</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45134</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45135</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45140</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45140</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45142</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>45148</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45149</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45149</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45149</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45152</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45152</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>45152</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45155</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45156</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45156</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45156</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>45156</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45156</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45161</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45161</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45161</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45161</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45161</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45163</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>45163</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>45166</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45166</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45166</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45166</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45167</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45167</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45167</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45167</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45168</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45168</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45168</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45168</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>45168</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45168</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45170</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45170</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45170</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45173</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45174</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45175</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45175</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43654,7 +43654,7 @@
         <v>45175</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45176</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45177</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45177</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45177</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45177</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45177</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45180</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45180</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45182</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>45182</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45182</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45183</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45184</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45184</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45184</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45187</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45187</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45187</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45187</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45187</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>45187</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45188</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45188</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45188</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>45188</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>45188</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45189</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45191</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45191</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45191</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45191</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>45191</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45191</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>45194</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>45195</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45196</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45196</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45198</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45198</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>45198</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45198</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45198</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45198</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45198</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45198</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45198</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45202</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45202</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>45202</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45202</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45204</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45204</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45205</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45205</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>45205</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>45205</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45208</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>45210</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47840,7 +47840,7 @@
         <v>45212</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45212</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45215</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45215</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45216</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45217</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>45218</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>45219</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45219</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45219</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45219</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45223</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45224</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>45225</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45225</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45225</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45225</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45226</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45226</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45226</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45230</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45230</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45230</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45230</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45230</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45236</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>45236</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>45237</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>45239</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>45243</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45243</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45243</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45244</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50002,7 +50002,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45247</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50121,7 +50121,7 @@
         <v>45247</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45247</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45249</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45253</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45253</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45253</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45253</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>45254</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45257</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45257</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45257</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45260</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45265</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45273</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45280</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51254,7 +51254,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51368,7 +51368,7 @@
         <v>45288</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45297</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>45301</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51601,7 +51601,7 @@
         <v>45301</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51658,7 +51658,7 @@
         <v>45302</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45303</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>45307</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45308</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45313</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51948,7 +51948,7 @@
         <v>45313</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45313</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>45313</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45317</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>45317</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52253,7 +52253,7 @@
         <v>45317</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52310,7 +52310,7 @@
         <v>45321</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52367,7 +52367,7 @@
         <v>45321</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         <v>45334</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45335</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45335</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52595,7 +52595,7 @@
         <v>45337</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45345</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -569,7 +569,7 @@
         <v>44322</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>44761</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>45204</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>44221</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>44937</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>45084</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>45162</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>44000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>44435</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>45013</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>45196</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45239</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>43452</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>43510</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>44188</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45099</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>43872</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44322</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44480</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>44831</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>44998</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>45061</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45121</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>45211</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>43389</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>43453</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>43581</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>43873</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44167</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44188</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44410</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44456</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44547</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>44560</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44571</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>44693</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44694</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>44706</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44825</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44832</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>44874</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>44888</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>45035</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>45041</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45089</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45093</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>45105</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45126</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>45140</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>45153</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>45189</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45197</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45208</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>43355</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>43363</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>43384</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>43385</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>43385</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>43385</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>43389</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>43389</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43403</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>43404</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>43404</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>43404</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>43411</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>43413</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>43416</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>43425</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>43427</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>43436</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>43447</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>43451</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>43452</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>43472</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>43472</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>43472</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>43473</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>43474</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>43494</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>43497</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>43500</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>43501</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>43502</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>43531</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>43532</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>43546</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>43551</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>43551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>43557</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>43566</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>43593</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>43594</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>43601</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>43605</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>43614</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>43628</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>43630</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>43630</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>43630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>43633</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>43649</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>43656</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>43662</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>43664</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>43681</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>43696</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>43698</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>43700</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>43705</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>43714</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43720</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>43731</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>43733</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>43734</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>43747</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>43770</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>43780</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>43782</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>43788</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>43791</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>43797</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>43798</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>43798</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>43798</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>43798</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>43801</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>43817</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>43819</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>43847</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>43847</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>43858</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>43860</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>43861</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>43861</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>43868</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>43868</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>43872</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>43873</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>43881</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>43881</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>43882</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>43887</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>43887</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>43892</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>43892</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>43893</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>43893</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>43894</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>43894</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>43895</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>43898</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>43900</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>43903</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>43903</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>43908</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>43910</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>43915</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>43918</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>43921</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>43921</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>43922</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>43923</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>43923</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43923</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>43923</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>43923</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>43923</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>43924</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>43949</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>43965</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>43965</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>43969</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>43978</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>43983</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>43983</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>43983</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>43983</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>43983</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13292,7 +13292,7 @@
         <v>43993</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>43999</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44000</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44000</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>44006</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44012</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44020</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>44022</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>44036</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44067</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44069</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>44069</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>44070</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>44081</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44085</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44085</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>44085</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44085</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>44089</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44090</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>44092</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44092</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>44092</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>44092</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44092</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>44092</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44092</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>44093</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>44097</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>44097</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>44103</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44103</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>44104</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>44113</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44116</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44116</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>44118</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44119</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44119</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>44120</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44123</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>44124</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>44127</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>44127</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44131</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44154</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44154</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44154</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44154</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>44159</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44165</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44166</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>44168</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44174</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44188</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44188</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44188</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44188</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44188</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44209</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44217</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44218</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44224</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>44237</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44244</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>44244</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>44249</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>44264</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>44274</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44281</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>44286</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>44291</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>44292</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>44292</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44299</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>44302</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>44316</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>44316</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>44316</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44316</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>44316</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44322</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>44322</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44322</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>44330</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44333</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>44336</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>44336</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>44337</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>44341</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44344</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44344</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>44358</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44362</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>44364</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>44368</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>44369</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>44369</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>44370</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>44370</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44370</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44370</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44376</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>44377</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>44377</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44386</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44386</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>44387</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>44393</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>44397</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44404</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44405</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44406</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>44413</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>44420</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>44431</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>44434</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44435</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>44435</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44439</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>44439</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>44441</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20750,7 +20750,7 @@
         <v>44447</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>44449</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>44452</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>44453</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>44456</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>44456</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44459</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>44459</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>44460</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44462</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44470</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>44476</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44477</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44477</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>44482</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44482</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>44482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>44502</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>44503</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>44508</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>44516</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44533</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>44536</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44543</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>44550</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22416,7 +22416,7 @@
         <v>44552</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>44560</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22535,7 +22535,7 @@
         <v>44560</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44572</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44579</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44579</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44581</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44590</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>44599</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>44600</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44602</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44603</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>44616</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>44643</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44652</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>44656</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>44658</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>44662</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44680</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>44685</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44687</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>44687</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>44700</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44701</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>44706</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44706</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>44708</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44711</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44715</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44720</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44720</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44725</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>44729</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44730</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44730</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44730</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44730</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44731</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44731</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44731</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44731</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>44731</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44731</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44731</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>44731</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>44730</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>44731</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>44731</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>44731</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25399,7 +25399,7 @@
         <v>44731</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44732</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>44733</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44741</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44743</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>44771</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>44771</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>44771</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44785</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>44789</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>44805</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44805</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44809</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44809</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44811</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>44813</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>44817</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>44817</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>44819</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>44820</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         <v>44820</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>44820</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>44825</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>44825</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
         <v>44825</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44826</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44826</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>44827</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44827</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
         <v>44827</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>44827</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>44830</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>44831</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44831</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44831</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44832</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44833</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44833</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44841</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44844</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44844</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44844</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44844</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44844</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44845</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28144,7 +28144,7 @@
         <v>44848</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44851</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28258,7 +28258,7 @@
         <v>44851</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>44853</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44854</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>44859</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28563,7 +28563,7 @@
         <v>44859</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44859</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>44859</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>44859</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>44859</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>44859</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>44861</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44862</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>44865</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>44867</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>44867</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>44869</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44869</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44869</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>44872</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44872</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         <v>44872</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>44872</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44874</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>44879</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>44879</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>44879</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>44880</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>44883</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44883</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>44886</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30336,7 +30336,7 @@
         <v>44887</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>44890</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44890</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44893</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44893</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44893</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>44895</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>44903</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>44907</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>44907</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>44915</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>44915</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>44915</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44916</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44923</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>44929</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>44929</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44929</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>44937</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31531,7 +31531,7 @@
         <v>44938</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>44939</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>44942</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>44950</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44957</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>44957</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44958</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>44958</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>44960</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44960</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>44960</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44960</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>44960</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>44963</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44964</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>44965</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44966</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44967</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>44970</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>44970</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>44970</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>44971</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44972</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>44974</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>44978</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>44981</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33088,7 +33088,7 @@
         <v>44994</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>44994</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>44998</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>45002</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45002</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45002</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45013</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45021</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>45030</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45034</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45034</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33750,7 +33750,7 @@
         <v>45034</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45034</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45043</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>45043</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>45043</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45044</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45044</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>45044</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45050</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>45051</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45054</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45055</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45056</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>45058</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45058</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45058</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45062</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45062</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34975,7 +34975,7 @@
         <v>45062</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45062</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35099,7 +35099,7 @@
         <v>45063</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         <v>45063</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>45063</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45063</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45063</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45063</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45063</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45063</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45068</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45068</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45068</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45068</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>45068</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45069</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45069</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45070</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45070</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45070</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36195,7 +36195,7 @@
         <v>45070</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45071</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>45078</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45079</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45079</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>45082</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45082</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36629,7 +36629,7 @@
         <v>45084</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45086</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45086</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>45089</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>45091</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>45093</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>45093</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45093</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45098</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45098</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45098</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>45098</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45099</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45099</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>45099</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45099</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45099</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45103</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45105</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>45105</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>45106</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45107</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45107</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45110</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45110</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45110</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>45110</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45112</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45112</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>45112</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45113</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45113</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45114</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45114</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>45114</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45114</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45117</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45118</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45119</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45119</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45119</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>45121</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>45121</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45125</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45125</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>45125</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45126</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45127</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45128</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45128</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45128</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>45131</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>45131</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45132</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40036,7 +40036,7 @@
         <v>45134</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45134</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45134</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>45134</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>45134</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45135</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45140</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45140</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>45142</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>45148</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45149</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45149</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45149</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45152</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45152</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>45152</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45155</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45156</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45156</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45156</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>45156</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>45156</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45161</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45161</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41680,7 +41680,7 @@
         <v>45161</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>45161</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>45161</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>45163</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>45163</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42166,7 +42166,7 @@
         <v>45166</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45166</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45166</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45166</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45167</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45167</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45167</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45167</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42662,7 +42662,7 @@
         <v>45168</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>45168</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45168</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45168</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>45168</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45168</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>45170</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43096,7 +43096,7 @@
         <v>45170</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43158,7 +43158,7 @@
         <v>45170</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45173</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45174</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45175</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45175</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43654,7 +43654,7 @@
         <v>45175</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45176</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45177</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45177</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45177</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45177</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45177</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45180</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45180</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45182</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>45182</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45182</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45183</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45184</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45184</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45184</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45187</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45187</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45187</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45187</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>45187</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>45187</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45188</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45188</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45188</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>45188</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>45188</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45189</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45191</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45504,7 +45504,7 @@
         <v>45191</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45191</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45752,7 +45752,7 @@
         <v>45191</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         <v>45191</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45876,7 +45876,7 @@
         <v>45191</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>45194</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>45195</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45196</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45196</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>45198</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45198</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46300,7 +46300,7 @@
         <v>45198</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>45198</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45198</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45198</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45198</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45198</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46672,7 +46672,7 @@
         <v>45198</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45202</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45202</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45202</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>45202</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45202</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>45204</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45204</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45205</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45205</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>45205</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>45205</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45208</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47597,7 +47597,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>45210</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47840,7 +47840,7 @@
         <v>45212</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45212</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45215</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45215</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45216</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45217</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48264,7 +48264,7 @@
         <v>45218</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>45219</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45219</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>45219</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45219</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45223</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45224</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>45225</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45225</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45225</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45225</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45226</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45226</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>45226</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45230</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45230</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45230</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45230</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45230</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45236</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>45236</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>45237</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>45239</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>45243</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45243</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45243</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45244</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45246</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50002,7 +50002,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45247</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50121,7 +50121,7 @@
         <v>45247</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45247</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>45249</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45253</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45253</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>45253</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>45253</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>45254</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45257</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45257</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45257</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45258</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45260</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45265</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45273</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45280</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51254,7 +51254,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51368,7 +51368,7 @@
         <v>45288</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45297</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>45301</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51601,7 +51601,7 @@
         <v>45301</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51658,7 +51658,7 @@
         <v>45302</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51715,7 +51715,7 @@
         <v>45303</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51772,7 +51772,7 @@
         <v>45307</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51834,7 +51834,7 @@
         <v>45308</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45313</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51948,7 +51948,7 @@
         <v>45313</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>45313</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>45313</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52139,7 +52139,7 @@
         <v>45317</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>45317</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52253,7 +52253,7 @@
         <v>45317</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52310,7 +52310,7 @@
         <v>45321</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52367,7 +52367,7 @@
         <v>45321</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         <v>45334</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45335</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45335</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52595,7 +52595,7 @@
         <v>45337</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45345</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -569,7 +569,7 @@
         <v>45348</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         <v>44322</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44761</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45204</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44221</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44937</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>45084</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45162</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44000</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>44435</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45013</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45196</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45239</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>43452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>43510</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>44188</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45099</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>43872</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44322</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>44480</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>44831</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44998</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45049</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45061</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45121</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>45211</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>43389</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>43453</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>43581</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>43873</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44167</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44188</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44410</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>44456</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44547</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44560</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44571</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>44693</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44694</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44706</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>44825</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44832</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45035</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45041</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45089</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45093</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>45105</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45126</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45140</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45153</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45189</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>45197</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45208</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>43355</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>43363</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>43384</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>43385</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>43385</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>43385</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>43389</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43389</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>43403</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43404</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>43404</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>43404</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>43411</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>43413</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>43416</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>43425</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>43427</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>43436</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>43447</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>43452</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>43472</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>43472</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>43472</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>43473</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43494</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>43497</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>43500</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>43501</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43502</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>43532</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>43546</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>43551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>43551</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>43557</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>43566</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>43593</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>43594</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>43605</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>43614</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>43628</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>43630</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>43630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>43630</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>43633</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>43636</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>43649</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>43656</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>43662</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>43664</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>43681</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>43696</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>43698</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>43700</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>43705</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>43714</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>43720</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43731</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43733</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43734</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43747</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43770</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43780</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43782</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>43788</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>43791</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>43797</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>43798</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>43798</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>43798</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>43798</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>43801</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>43817</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>43819</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>43847</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43847</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43858</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>43860</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>43861</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>43861</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>43868</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>43868</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>43872</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>43873</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43881</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>43881</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>43882</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>43887</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>43887</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>43892</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>43892</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>43893</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>43893</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43894</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43894</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43898</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>43900</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>43903</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43903</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43908</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>43910</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>43915</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>43918</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43921</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>43921</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>43922</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>43923</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>43923</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>43923</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>43923</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43923</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>43923</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>43924</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>43949</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>43965</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>43965</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>43969</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>43978</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>43983</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>43983</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>43983</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>43983</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>43983</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>43993</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43999</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44000</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44000</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>44006</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>44012</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44020</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44022</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>44036</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>44067</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44069</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>44069</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>44070</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44081</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44085</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>44085</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44085</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44085</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>44089</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44090</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44092</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44092</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44092</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44092</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>44092</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44092</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>44092</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>44093</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>44097</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44097</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>44103</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44104</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44113</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44116</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44116</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>44118</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>44119</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44119</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>44120</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44123</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>44124</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>44127</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44127</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44131</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>44154</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44154</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44154</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>44159</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44165</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44166</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>44168</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>44174</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>44188</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>44188</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>44188</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44188</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>44188</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>44209</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>44217</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>44218</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44224</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>44237</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>44244</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17379,7 +17379,7 @@
         <v>44244</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>44249</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>44264</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>44274</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>44281</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>44286</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44291</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44292</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>44292</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44299</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>44302</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>44316</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44316</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>44316</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44316</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>44316</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>44322</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>44322</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>44322</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>44330</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>44333</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44333</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44336</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>44336</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>44337</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44341</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44344</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44344</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>44358</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>44362</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>44364</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>44368</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>44369</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>44369</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44370</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44370</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44370</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44377</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>44377</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44386</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>44386</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>44387</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>44393</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44397</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44404</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44405</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>44406</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>44413</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44431</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44434</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44435</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>44435</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44439</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44439</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44441</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44447</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44449</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>44452</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44453</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44456</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>44456</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>44459</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44459</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44460</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44462</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44470</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>44476</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44477</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44477</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44482</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44482</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44502</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44503</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>44508</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>44515</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>44516</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>44516</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>44533</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>44536</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>44543</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>44550</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>44552</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>44560</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>44560</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44572</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44579</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44579</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44581</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>44590</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>44599</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44600</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>44602</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>44603</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>44616</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>44643</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>44652</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>44656</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>44658</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>44662</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>44680</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>44685</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44687</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44687</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44700</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>44701</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44706</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44706</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44708</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44711</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>44715</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44720</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44720</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44725</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44729</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>44730</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>44730</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44730</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>44730</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44731</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>44731</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>44731</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>44731</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>44731</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>44731</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44731</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44731</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44730</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>44731</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44731</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>44731</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>44731</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>44732</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44733</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44741</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44743</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44771</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44771</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>44771</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>44785</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44789</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>44805</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44805</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44809</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>44809</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>44811</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44813</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44817</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44817</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>44819</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44820</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44820</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>44820</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>44825</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>44825</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>44825</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44826</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>44826</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44827</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44827</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>44827</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>44827</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44830</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44831</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>44831</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>44831</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>44832</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44833</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44833</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>44841</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>44844</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44844</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>44844</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44844</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44844</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>44845</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44848</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>44851</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>44851</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44852</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44853</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44854</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>44859</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44859</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>44859</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44859</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44859</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44859</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>44861</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>44862</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>44867</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>44867</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>44869</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>44869</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44869</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44872</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>44872</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>44872</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44872</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>44874</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>44879</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>44879</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>44879</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>44880</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>44883</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>44883</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>44886</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>44887</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>44890</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>44890</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44893</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>44893</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>44893</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44895</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44900</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44903</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>44907</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44907</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44915</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44915</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44915</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44916</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>44923</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>44929</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>44929</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>44929</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44937</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>44938</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44939</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44942</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44950</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44957</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>44957</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>44958</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44958</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44960</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>44960</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>44960</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>44960</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>44960</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>44963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44964</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>44965</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44966</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44967</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44970</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>44970</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44970</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>44971</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>44972</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>44974</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>44978</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>44981</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>44994</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>44994</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44998</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45002</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>45002</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>45002</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45013</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>45021</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45030</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45034</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45034</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>45034</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45034</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45043</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34056,7 +34056,7 @@
         <v>45043</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>45043</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>45044</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45044</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>45044</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>45050</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>45051</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45054</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>45055</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45056</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45058</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>45058</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45058</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45062</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45062</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>45062</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45062</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45063</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45063</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45063</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>45063</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>45063</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45063</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45063</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45063</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35710,7 +35710,7 @@
         <v>45068</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45068</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>45068</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>45068</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>45068</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36005,7 +36005,7 @@
         <v>45069</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45069</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45070</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45070</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45070</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45070</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>45071</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45078</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45079</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45079</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45082</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45082</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45084</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45086</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45086</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>45089</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45091</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37059,7 +37059,7 @@
         <v>45093</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45093</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>45093</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45098</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>45098</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>45098</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45098</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45099</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37555,7 +37555,7 @@
         <v>45099</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>45099</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45099</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45099</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45105</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>45105</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>45106</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>45107</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>45107</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>45110</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>45110</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>45110</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>45110</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>45112</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45112</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>45113</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>45113</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45114</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45114</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45114</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45114</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>45117</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>45118</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45119</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45119</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45119</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39365,7 +39365,7 @@
         <v>45121</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>45121</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>45125</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
         <v>45125</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45125</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45126</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45127</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>45128</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>45128</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>45128</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>45131</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45131</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45132</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>45134</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>45134</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>45134</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>45134</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45134</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>45135</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>45140</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>45140</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45142</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45148</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45149</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45149</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>45149</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45152</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45152</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>45152</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>45155</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>45156</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>45156</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>45156</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45156</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45156</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45161</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45161</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45161</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41800,7 +41800,7 @@
         <v>45161</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>45161</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>45161</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>45163</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>45163</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45166</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45166</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45166</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45166</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>45166</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>45167</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>45167</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         <v>45167</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45168</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>45168</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45168</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45168</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45168</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45168</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>45170</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>45170</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43526,7 +43526,7 @@
         <v>45173</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43588,7 +43588,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45175</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43712,7 +43712,7 @@
         <v>45175</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45175</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>45176</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45177</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45177</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>45177</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45177</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45177</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>45180</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45180</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44327,7 +44327,7 @@
         <v>45182</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>45182</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45182</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45183</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45184</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45184</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45184</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45187</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45187</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>45187</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>45187</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>45187</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>45187</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45188</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         <v>45188</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45188</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>45188</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45505,7 +45505,7 @@
         <v>45189</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45191</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>45191</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45810,7 +45810,7 @@
         <v>45191</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>45191</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>45191</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>45191</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46058,7 +46058,7 @@
         <v>45194</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46115,7 +46115,7 @@
         <v>45195</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46172,7 +46172,7 @@
         <v>45196</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>45196</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46296,7 +46296,7 @@
         <v>45198</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45198</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>45198</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45198</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>45198</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>45198</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>45198</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45198</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46792,7 +46792,7 @@
         <v>45198</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>45202</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45202</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45202</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45202</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45202</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45204</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45204</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45205</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>45205</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45205</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45205</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47531,7 +47531,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47717,7 +47717,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47779,7 +47779,7 @@
         <v>45208</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47836,7 +47836,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45212</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45212</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45215</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45215</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45216</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45217</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45218</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45219</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>45219</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48565,7 +48565,7 @@
         <v>45219</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         <v>45219</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>45223</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>45224</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>45225</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45225</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45225</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45225</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49046,7 +49046,7 @@
         <v>45226</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>45226</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45226</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45230</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45230</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45230</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45230</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45230</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>45236</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45236</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>45237</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>45239</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45243</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49837,7 +49837,7 @@
         <v>45243</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>45243</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45244</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50122,7 +50122,7 @@
         <v>45246</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>45247</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45247</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45247</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50365,7 +50365,7 @@
         <v>45249</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50422,7 +50422,7 @@
         <v>45253</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45253</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>45253</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45253</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50794,7 +50794,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50851,7 +50851,7 @@
         <v>45257</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45257</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45257</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45260</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45265</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51198,7 +51198,7 @@
         <v>45273</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51317,7 +51317,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45280</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45288</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45297</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45301</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>45301</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51778,7 +51778,7 @@
         <v>45302</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45303</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>45307</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45308</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52011,7 +52011,7 @@
         <v>45313</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>45313</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52145,7 +52145,7 @@
         <v>45313</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45313</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45317</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52316,7 +52316,7 @@
         <v>45317</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>45317</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52423,14 +52423,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 3809-2024</t>
+          <t>A 3687-2024</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52443,7 +52443,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -52480,14 +52480,14 @@
     <row r="833" ht="15" customHeight="1">
       <c r="A833" t="inlineStr">
         <is>
-          <t>A 3687-2024</t>
+          <t>A 3809-2024</t>
         </is>
       </c>
       <c r="B833" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52500,7 +52500,7 @@
         </is>
       </c>
       <c r="G833" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="H833" t="n">
         <v>0</v>
@@ -52544,7 +52544,7 @@
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
         <v>45335</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52658,7 +52658,7 @@
         <v>45335</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52715,7 +52715,7 @@
         <v>45337</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>45345</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z838"/>
+  <dimension ref="A1:Z839"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45348</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         <v>44322</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44761</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45204</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44221</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44937</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>45084</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45162</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44000</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>44435</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45013</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45196</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45239</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>43452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>43510</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>44188</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45099</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>43872</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44322</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>44480</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>44831</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44998</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45049</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45061</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45121</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>45211</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>43389</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>43453</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>43581</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>43873</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44167</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44188</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44410</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>44456</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44547</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44560</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44571</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>44693</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44694</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44706</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>44825</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44832</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45035</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45041</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45089</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45093</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>45105</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45126</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45140</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45153</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45189</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>45197</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45208</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>43355</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>43363</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>43384</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>43385</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>43385</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>43385</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>43389</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43389</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>43403</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43404</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>43404</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>43404</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>43411</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>43413</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>43416</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>43425</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>43427</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>43436</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>43447</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>43452</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>43472</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>43472</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>43472</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>43473</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43494</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>43497</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>43500</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>43501</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43502</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>43532</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>43546</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>43551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>43551</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>43557</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>43566</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>43593</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>43594</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>43605</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>43614</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>43628</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>43630</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>43630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>43630</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>43633</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>43636</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>43649</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>43656</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>43662</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>43664</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>43681</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>43696</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>43698</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>43700</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>43705</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>43714</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>43720</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43731</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43733</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43734</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43747</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43770</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43780</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43782</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>43788</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>43791</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>43797</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>43798</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>43798</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>43798</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>43798</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>43801</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>43817</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>43819</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>43847</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43847</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43858</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>43860</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>43861</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>43861</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>43868</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>43868</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>43872</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>43873</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43881</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>43881</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>43882</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>43887</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>43887</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>43892</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>43892</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>43893</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>43893</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43894</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43894</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43898</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>43900</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>43903</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43903</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43908</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>43910</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>43915</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>43918</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43921</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>43921</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>43922</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>43923</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>43923</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>43923</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>43923</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43923</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>43923</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>43924</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>43949</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>43965</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>43965</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>43969</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>43978</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>43983</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>43983</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>43983</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>43983</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>43983</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>43993</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43999</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44000</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44000</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>44006</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>44012</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44020</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44022</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>44036</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>44067</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44069</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>44069</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>44070</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44081</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44085</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>44085</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44085</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44085</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>44089</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44090</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44092</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44092</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44092</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44092</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>44092</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44092</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>44092</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>44093</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>44097</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44097</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>44103</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44104</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44113</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44116</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44116</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>44118</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>44119</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44119</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>44120</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44123</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>44124</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>44127</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44127</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44131</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>44154</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44154</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44154</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>44159</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44165</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44166</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>44168</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>44174</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>44188</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>44188</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>44188</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44188</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>44188</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>44209</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>44217</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>44218</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44224</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>44237</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>44244</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17379,7 +17379,7 @@
         <v>44244</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>44249</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>44264</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>44274</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>44281</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>44286</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44291</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44292</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>44292</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44299</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>44302</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>44316</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44316</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>44316</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44316</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>44316</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>44322</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>44322</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>44322</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>44330</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>44333</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44333</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44336</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>44336</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>44337</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44341</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44344</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44344</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>44358</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>44362</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>44364</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>44368</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>44369</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>44369</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44370</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44370</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44370</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44377</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>44377</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44386</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>44386</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>44387</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>44393</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44397</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44404</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44405</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>44406</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>44413</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44431</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44434</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44435</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>44435</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44439</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44439</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44441</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44447</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44449</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>44452</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44453</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44456</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>44456</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>44459</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44459</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44460</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44462</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44470</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>44476</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44477</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44477</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44482</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44482</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44502</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44503</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>44508</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>44515</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>44516</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>44516</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>44533</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>44536</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>44543</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>44550</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>44552</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>44560</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>44560</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44572</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44579</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44579</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44581</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>44590</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>44599</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44600</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>44602</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>44603</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>44616</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>44643</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>44652</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>44656</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>44658</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>44662</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>44680</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>44685</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44687</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44687</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44700</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>44701</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44706</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44706</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44708</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44711</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>44715</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44720</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44720</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44725</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44729</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>44730</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>44730</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44730</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>44730</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44731</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>44731</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>44731</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>44731</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>44731</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>44731</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44731</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44731</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44730</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>44731</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44731</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>44731</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>44731</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>44732</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44733</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44741</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44743</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44771</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44771</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>44771</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>44785</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44789</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>44805</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44805</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44809</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>44809</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>44811</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44813</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44817</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44817</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>44819</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44820</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44820</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>44820</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>44825</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>44825</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>44825</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44826</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>44826</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44827</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44827</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>44827</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>44827</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44830</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44831</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>44831</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>44831</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>44832</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44833</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44833</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>44841</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>44844</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44844</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>44844</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44844</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44844</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>44845</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44848</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>44851</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>44851</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44852</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44853</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44854</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>44859</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44859</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>44859</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44859</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44859</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44859</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>44861</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>44862</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>44867</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>44867</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>44869</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>44869</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44869</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44872</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>44872</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>44872</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44872</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>44874</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>44879</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>44879</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>44879</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>44880</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>44883</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>44883</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>44886</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>44887</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>44890</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>44890</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44893</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>44893</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>44893</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44895</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44900</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44903</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>44907</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44907</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44915</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44915</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44915</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44916</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>44923</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>44929</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>44929</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>44929</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44937</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>44938</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44939</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44942</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44950</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44957</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>44957</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>44958</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44958</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44960</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>44960</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>44960</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>44960</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>44960</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>44963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44964</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>44965</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44966</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44967</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44970</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>44970</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44970</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>44971</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>44972</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>44974</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>44978</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>44981</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>44994</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>44994</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44998</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45002</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>45002</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>45002</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45013</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>45021</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45030</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45034</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45034</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>45034</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45034</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45043</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34056,7 +34056,7 @@
         <v>45043</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>45043</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>45044</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45044</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>45044</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>45050</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>45051</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45054</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>45055</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45056</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45058</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>45058</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45058</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45062</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45062</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>45062</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45062</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45063</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45063</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45063</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>45063</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>45063</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45063</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45063</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45063</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35710,7 +35710,7 @@
         <v>45068</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45068</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>45068</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>45068</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>45068</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36005,7 +36005,7 @@
         <v>45069</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45069</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45070</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45070</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45070</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45070</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>45071</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45078</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45079</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45079</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45082</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45082</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45084</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45086</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45086</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>45089</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45091</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37059,7 +37059,7 @@
         <v>45093</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45093</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>45093</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45098</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>45098</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>45098</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45098</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45099</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37555,7 +37555,7 @@
         <v>45099</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>45099</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45099</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45099</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45105</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>45105</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>45106</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>45107</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>45107</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>45110</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>45110</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>45110</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>45110</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>45112</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45112</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>45113</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>45113</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45114</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45114</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45114</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45114</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>45117</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>45118</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45119</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45119</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45119</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39365,7 +39365,7 @@
         <v>45121</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>45121</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>45125</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
         <v>45125</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45125</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45126</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45127</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>45128</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>45128</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>45128</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>45131</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45131</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45132</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>45134</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>45134</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>45134</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>45134</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45134</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>45135</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>45140</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>45140</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45142</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45148</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45149</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45149</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>45149</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45152</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45152</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>45152</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>45155</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>45156</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>45156</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>45156</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45156</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45156</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45161</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45161</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45161</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41800,7 +41800,7 @@
         <v>45161</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>45161</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>45161</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>45163</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>45163</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45166</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45166</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45166</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45166</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>45166</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>45167</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>45167</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         <v>45167</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45168</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>45168</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45168</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45168</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45168</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45168</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>45170</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>45170</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43526,7 +43526,7 @@
         <v>45173</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43588,7 +43588,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45175</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43712,7 +43712,7 @@
         <v>45175</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45175</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>45176</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45177</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45177</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>45177</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45177</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45177</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>45180</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45180</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44327,7 +44327,7 @@
         <v>45182</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>45182</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45182</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45183</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45184</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45184</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45184</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45187</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45187</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>45187</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>45187</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>45187</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>45187</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45188</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         <v>45188</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45188</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>45188</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45505,7 +45505,7 @@
         <v>45189</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45191</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>45191</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45810,7 +45810,7 @@
         <v>45191</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>45191</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>45191</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>45191</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46058,7 +46058,7 @@
         <v>45194</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46115,7 +46115,7 @@
         <v>45195</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46172,7 +46172,7 @@
         <v>45196</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>45196</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46296,7 +46296,7 @@
         <v>45198</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45198</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>45198</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45198</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>45198</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>45198</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>45198</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45198</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46792,7 +46792,7 @@
         <v>45198</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>45202</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45202</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45202</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45202</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45202</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45204</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45204</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45205</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>45205</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45205</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45205</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47531,7 +47531,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47717,7 +47717,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47779,7 +47779,7 @@
         <v>45208</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47836,7 +47836,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45212</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45212</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45215</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45215</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45216</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45217</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45218</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45219</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>45219</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48565,7 +48565,7 @@
         <v>45219</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         <v>45219</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>45223</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>45224</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>45225</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45225</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45225</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45225</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49046,7 +49046,7 @@
         <v>45226</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>45226</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45226</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45230</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45230</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45230</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45230</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45230</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>45236</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45236</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>45237</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>45239</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45243</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49837,7 +49837,7 @@
         <v>45243</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>45243</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45244</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50122,7 +50122,7 @@
         <v>45246</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>45247</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45247</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45247</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50365,7 +50365,7 @@
         <v>45249</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50422,7 +50422,7 @@
         <v>45253</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45253</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>45253</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45253</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50794,7 +50794,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50851,7 +50851,7 @@
         <v>45257</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45257</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45257</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45260</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45265</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51198,7 +51198,7 @@
         <v>45273</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51317,7 +51317,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45280</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45288</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45297</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45301</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>45301</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51778,7 +51778,7 @@
         <v>45302</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45303</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>45307</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45308</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52011,7 +52011,7 @@
         <v>45313</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>45313</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52145,7 +52145,7 @@
         <v>45313</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45313</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45317</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52316,7 +52316,7 @@
         <v>45317</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>45317</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45321</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52487,7 +52487,7 @@
         <v>45321</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
         <v>45335</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52658,7 +52658,7 @@
         <v>45335</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52715,7 +52715,7 @@
         <v>45337</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52762,7 +52762,7 @@
       </c>
       <c r="R837" s="2" t="inlineStr"/>
     </row>
-    <row r="838">
+    <row r="838" ht="15" customHeight="1">
       <c r="A838" t="inlineStr">
         <is>
           <t>A 7317-2024</t>
@@ -52772,7 +52772,7 @@
         <v>45345</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52818,6 +52818,63 @@
         <v>0</v>
       </c>
       <c r="R838" s="2" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>A 7996-2024</t>
+        </is>
+      </c>
+      <c r="B839" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="C839" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="G839" t="n">
+        <v>1</v>
+      </c>
+      <c r="H839" t="n">
+        <v>0</v>
+      </c>
+      <c r="I839" t="n">
+        <v>0</v>
+      </c>
+      <c r="J839" t="n">
+        <v>0</v>
+      </c>
+      <c r="K839" t="n">
+        <v>0</v>
+      </c>
+      <c r="L839" t="n">
+        <v>0</v>
+      </c>
+      <c r="M839" t="n">
+        <v>0</v>
+      </c>
+      <c r="N839" t="n">
+        <v>0</v>
+      </c>
+      <c r="O839" t="n">
+        <v>0</v>
+      </c>
+      <c r="P839" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q839" t="n">
+        <v>0</v>
+      </c>
+      <c r="R839" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z839"/>
+  <dimension ref="A1:Z843"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45348</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         <v>44322</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44761</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45204</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44221</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44937</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>45084</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45162</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44000</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>44435</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45013</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45196</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45239</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>43452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>43510</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>44188</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45099</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>43872</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44322</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>44480</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>44831</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44998</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45049</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45061</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45121</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>45211</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>43389</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>43453</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>43581</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>43873</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44167</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44188</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44410</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>44456</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44547</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44560</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44571</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>44693</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44694</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44706</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>44825</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44832</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45035</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45041</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45089</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45093</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>45105</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45126</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45140</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45153</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45189</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>45197</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45208</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>43355</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>43363</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>43384</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>43385</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>43385</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>43385</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>43389</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43389</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>43403</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43404</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>43404</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>43404</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>43411</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>43413</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>43416</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>43425</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>43427</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>43436</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>43447</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>43452</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>43472</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>43472</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>43472</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>43473</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43494</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>43497</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>43500</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>43501</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43502</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>43532</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>43546</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>43551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>43551</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>43557</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>43566</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>43593</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>43594</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>43605</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>43614</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>43628</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>43630</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>43630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>43630</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>43633</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>43636</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>43649</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>43656</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>43662</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>43664</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>43681</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>43696</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>43698</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>43700</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>43705</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>43714</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>43720</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43731</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43733</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43734</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43747</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43770</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43780</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43782</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>43788</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>43791</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>43797</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>43798</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>43798</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>43798</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>43798</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>43801</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>43817</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>43819</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>43847</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43847</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43858</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>43860</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>43861</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>43861</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>43868</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>43868</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>43872</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>43873</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43881</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>43881</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>43882</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>43887</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>43887</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>43892</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>43892</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>43893</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>43893</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43894</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43894</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43898</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>43900</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>43903</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43903</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43908</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>43910</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>43915</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>43918</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43921</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>43921</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>43922</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>43923</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>43923</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>43923</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>43923</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43923</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>43923</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>43924</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>43949</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>43965</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>43965</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>43969</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>43978</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>43983</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>43983</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>43983</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>43983</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>43983</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>43993</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43999</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44000</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44000</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>44006</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>44012</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44020</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44022</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>44036</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>44067</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44069</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>44069</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>44070</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44081</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44085</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>44085</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44085</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44085</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>44089</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44090</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44092</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44092</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44092</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44092</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>44092</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44092</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>44092</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>44093</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>44097</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44097</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>44103</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44104</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44113</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44116</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44116</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>44118</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>44119</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44119</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>44120</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44123</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>44124</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>44127</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44127</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44131</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>44154</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44154</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44154</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>44159</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44165</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44166</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>44168</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>44174</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>44188</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>44188</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>44188</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44188</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>44188</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>44209</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>44217</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>44218</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44224</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>44237</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>44244</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17379,7 +17379,7 @@
         <v>44244</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>44249</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>44264</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>44274</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>44281</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>44286</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44291</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44292</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>44292</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44299</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>44302</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>44316</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44316</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>44316</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44316</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>44316</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>44322</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>44322</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>44322</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>44330</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>44333</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44333</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44336</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>44336</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>44337</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44341</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44344</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44344</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>44358</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>44362</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>44364</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>44368</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>44369</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>44369</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44370</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44370</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44370</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44377</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>44377</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44386</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>44386</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>44387</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>44393</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44397</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44404</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44405</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>44406</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>44413</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44431</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44434</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44435</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>44435</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44439</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44439</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44441</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44447</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44449</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>44452</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44453</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44456</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>44456</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>44459</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44459</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44460</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44462</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44470</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>44476</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44477</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44477</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44482</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44482</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44502</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44503</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>44508</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>44515</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>44516</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>44516</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>44533</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>44536</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>44543</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>44550</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>44552</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>44560</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>44560</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44572</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44579</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44579</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44581</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>44590</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>44599</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44600</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>44602</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>44603</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>44616</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>44643</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>44652</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>44656</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>44658</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>44662</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>44680</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>44685</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44687</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44687</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44700</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>44701</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44706</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44706</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44708</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44711</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>44715</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44720</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44720</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44725</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44729</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>44730</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>44730</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44730</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>44730</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44731</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>44731</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>44731</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>44731</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>44731</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>44731</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44731</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44731</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44730</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>44731</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44731</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>44731</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>44731</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>44732</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44733</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44741</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44743</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44771</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44771</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>44771</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>44785</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44789</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>44805</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44805</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44809</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>44809</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>44811</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44813</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44817</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44817</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>44819</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44820</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44820</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>44820</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>44825</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>44825</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>44825</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44826</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>44826</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44827</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44827</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>44827</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>44827</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44830</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44831</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>44831</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>44831</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>44832</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44833</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44833</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>44841</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>44844</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44844</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>44844</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44844</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44844</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>44845</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44848</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>44851</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>44851</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44852</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44853</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44854</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>44859</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44859</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>44859</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44859</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44859</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44859</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>44861</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>44862</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>44867</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>44867</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>44869</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>44869</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44869</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44872</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>44872</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>44872</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44872</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>44874</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>44879</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>44879</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>44879</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>44880</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>44883</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>44883</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>44886</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>44887</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>44890</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>44890</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44893</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>44893</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>44893</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44895</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44900</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44903</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>44907</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44907</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44915</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44915</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44915</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44916</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>44923</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>44929</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>44929</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>44929</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44937</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>44938</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44939</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44942</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44950</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44957</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>44957</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>44958</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44958</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44960</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>44960</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>44960</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>44960</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>44960</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>44963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44964</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>44965</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44966</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44967</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44970</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>44970</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44970</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>44971</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>44972</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>44974</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>44978</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>44981</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>44994</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>44994</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44998</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45002</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>45002</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>45002</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45013</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>45021</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45030</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45034</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45034</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>45034</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45034</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45043</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34056,7 +34056,7 @@
         <v>45043</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>45043</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>45044</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45044</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>45044</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>45050</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>45051</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45054</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>45055</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45056</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45058</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>45058</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45058</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45062</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45062</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>45062</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45062</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45063</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45063</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45063</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>45063</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>45063</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45063</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45063</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45063</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35710,7 +35710,7 @@
         <v>45068</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45068</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>45068</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>45068</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>45068</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36005,7 +36005,7 @@
         <v>45069</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45069</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45070</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45070</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45070</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45070</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>45071</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45078</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45079</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45079</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45082</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45082</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45084</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45086</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45086</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>45089</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45091</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37059,7 +37059,7 @@
         <v>45093</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45093</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>45093</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45098</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>45098</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>45098</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45098</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45099</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37555,7 +37555,7 @@
         <v>45099</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>45099</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45099</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45099</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45105</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>45105</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>45106</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>45107</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>45107</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>45110</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>45110</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>45110</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>45110</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>45112</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45112</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>45113</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>45113</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45114</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45114</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45114</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45114</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>45117</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>45118</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45119</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45119</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45119</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39365,7 +39365,7 @@
         <v>45121</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>45121</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>45125</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
         <v>45125</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45125</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45126</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45127</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>45128</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>45128</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>45128</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>45131</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45131</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45132</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>45134</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>45134</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>45134</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>45134</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45134</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>45135</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>45140</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>45140</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45142</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45148</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45149</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45149</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>45149</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45152</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45152</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>45152</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>45155</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>45156</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>45156</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>45156</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45156</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45156</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45161</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45161</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45161</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41800,7 +41800,7 @@
         <v>45161</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>45161</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>45161</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>45163</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>45163</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45166</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45166</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45166</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45166</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>45166</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>45167</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>45167</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         <v>45167</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45168</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>45168</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45168</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45168</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45168</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45168</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>45170</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>45170</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43526,7 +43526,7 @@
         <v>45173</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43588,7 +43588,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45175</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43712,7 +43712,7 @@
         <v>45175</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45175</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>45176</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45177</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45177</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>45177</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45177</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45177</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>45180</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45180</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44327,7 +44327,7 @@
         <v>45182</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>45182</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45182</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45183</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45184</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45184</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45184</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45187</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45187</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>45187</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>45187</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>45187</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>45187</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45188</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         <v>45188</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45188</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>45188</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45505,7 +45505,7 @@
         <v>45189</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45191</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>45191</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45810,7 +45810,7 @@
         <v>45191</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>45191</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>45191</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>45191</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46058,7 +46058,7 @@
         <v>45194</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46115,7 +46115,7 @@
         <v>45195</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46172,7 +46172,7 @@
         <v>45196</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>45196</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46296,7 +46296,7 @@
         <v>45198</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45198</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>45198</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45198</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>45198</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>45198</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>45198</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45198</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46792,7 +46792,7 @@
         <v>45198</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>45202</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45202</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45202</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45202</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45202</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45204</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45204</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45205</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>45205</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45205</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45205</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47531,7 +47531,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47717,7 +47717,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47779,7 +47779,7 @@
         <v>45208</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47836,7 +47836,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45212</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45212</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45215</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45215</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45216</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45217</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45218</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45219</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>45219</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48565,7 +48565,7 @@
         <v>45219</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         <v>45219</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>45223</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>45224</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>45225</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45225</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45225</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45225</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49046,7 +49046,7 @@
         <v>45226</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>45226</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45226</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45230</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45230</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45230</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45230</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45230</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>45236</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45236</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>45237</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>45239</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45243</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49837,7 +49837,7 @@
         <v>45243</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>45243</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45244</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50122,7 +50122,7 @@
         <v>45246</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>45247</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45247</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45247</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50365,7 +50365,7 @@
         <v>45249</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50422,7 +50422,7 @@
         <v>45253</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45253</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>45253</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45253</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50794,7 +50794,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50851,7 +50851,7 @@
         <v>45257</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45257</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45257</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45260</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45265</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51198,7 +51198,7 @@
         <v>45273</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51317,7 +51317,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45280</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45288</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45297</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45301</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>45301</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51778,7 +51778,7 @@
         <v>45302</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45303</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>45307</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45308</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52011,7 +52011,7 @@
         <v>45313</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>45313</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52145,7 +52145,7 @@
         <v>45313</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45313</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45317</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52316,7 +52316,7 @@
         <v>45317</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>45317</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45321</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52487,7 +52487,7 @@
         <v>45321</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
         <v>45335</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52658,7 +52658,7 @@
         <v>45335</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52715,7 +52715,7 @@
         <v>45337</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>45345</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52819,62 +52819,330 @@
       </c>
       <c r="R838" s="2" t="inlineStr"/>
     </row>
-    <row r="839">
+    <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
+          <t>A 8162-2024</t>
+        </is>
+      </c>
+      <c r="B839" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C839" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="G839" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H839" t="n">
+        <v>0</v>
+      </c>
+      <c r="I839" t="n">
+        <v>0</v>
+      </c>
+      <c r="J839" t="n">
+        <v>0</v>
+      </c>
+      <c r="K839" t="n">
+        <v>0</v>
+      </c>
+      <c r="L839" t="n">
+        <v>0</v>
+      </c>
+      <c r="M839" t="n">
+        <v>0</v>
+      </c>
+      <c r="N839" t="n">
+        <v>0</v>
+      </c>
+      <c r="O839" t="n">
+        <v>0</v>
+      </c>
+      <c r="P839" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q839" t="n">
+        <v>0</v>
+      </c>
+      <c r="R839" s="2" t="inlineStr"/>
+      <c r="U839">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/knärot/A 8162-2024 karta knärot.png", "A 8162-2024")</f>
+        <v/>
+      </c>
+      <c r="V839">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomål/A 8162-2024 FSC-klagomål.docx", "A 8162-2024")</f>
+        <v/>
+      </c>
+      <c r="W839">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomålsmail/A 8162-2024 FSC-klagomål mail.docx", "A 8162-2024")</f>
+        <v/>
+      </c>
+      <c r="X839">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsyn/A 8162-2024 tillsynsbegäran.docx", "A 8162-2024")</f>
+        <v/>
+      </c>
+      <c r="Y839">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsynsmail/A 8162-2024 tillsynsbegäran mail.docx", "A 8162-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="840" ht="15" customHeight="1">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>A 8172-2024</t>
+        </is>
+      </c>
+      <c r="B840" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C840" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="G840" t="n">
+        <v>2</v>
+      </c>
+      <c r="H840" t="n">
+        <v>0</v>
+      </c>
+      <c r="I840" t="n">
+        <v>0</v>
+      </c>
+      <c r="J840" t="n">
+        <v>0</v>
+      </c>
+      <c r="K840" t="n">
+        <v>0</v>
+      </c>
+      <c r="L840" t="n">
+        <v>0</v>
+      </c>
+      <c r="M840" t="n">
+        <v>0</v>
+      </c>
+      <c r="N840" t="n">
+        <v>0</v>
+      </c>
+      <c r="O840" t="n">
+        <v>0</v>
+      </c>
+      <c r="P840" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q840" t="n">
+        <v>0</v>
+      </c>
+      <c r="R840" s="2" t="inlineStr"/>
+    </row>
+    <row r="841" ht="15" customHeight="1">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>A 8170-2024</t>
+        </is>
+      </c>
+      <c r="B841" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C841" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="G841" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H841" t="n">
+        <v>0</v>
+      </c>
+      <c r="I841" t="n">
+        <v>0</v>
+      </c>
+      <c r="J841" t="n">
+        <v>0</v>
+      </c>
+      <c r="K841" t="n">
+        <v>0</v>
+      </c>
+      <c r="L841" t="n">
+        <v>0</v>
+      </c>
+      <c r="M841" t="n">
+        <v>0</v>
+      </c>
+      <c r="N841" t="n">
+        <v>0</v>
+      </c>
+      <c r="O841" t="n">
+        <v>0</v>
+      </c>
+      <c r="P841" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q841" t="n">
+        <v>0</v>
+      </c>
+      <c r="R841" s="2" t="inlineStr"/>
+    </row>
+    <row r="842" ht="15" customHeight="1">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>A 8175-2024</t>
+        </is>
+      </c>
+      <c r="B842" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C842" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="G842" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H842" t="n">
+        <v>0</v>
+      </c>
+      <c r="I842" t="n">
+        <v>0</v>
+      </c>
+      <c r="J842" t="n">
+        <v>0</v>
+      </c>
+      <c r="K842" t="n">
+        <v>0</v>
+      </c>
+      <c r="L842" t="n">
+        <v>0</v>
+      </c>
+      <c r="M842" t="n">
+        <v>0</v>
+      </c>
+      <c r="N842" t="n">
+        <v>0</v>
+      </c>
+      <c r="O842" t="n">
+        <v>0</v>
+      </c>
+      <c r="P842" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q842" t="n">
+        <v>0</v>
+      </c>
+      <c r="R842" s="2" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
           <t>A 7996-2024</t>
         </is>
       </c>
-      <c r="B839" s="1" t="n">
+      <c r="B843" s="1" t="n">
         <v>45350</v>
       </c>
-      <c r="C839" s="1" t="n">
-        <v>45351</v>
-      </c>
-      <c r="D839" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="E839" t="inlineStr">
-        <is>
-          <t>LUDVIKA</t>
-        </is>
-      </c>
-      <c r="G839" t="n">
+      <c r="C843" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="G843" t="n">
         <v>1</v>
       </c>
-      <c r="H839" t="n">
-        <v>0</v>
-      </c>
-      <c r="I839" t="n">
-        <v>0</v>
-      </c>
-      <c r="J839" t="n">
-        <v>0</v>
-      </c>
-      <c r="K839" t="n">
-        <v>0</v>
-      </c>
-      <c r="L839" t="n">
-        <v>0</v>
-      </c>
-      <c r="M839" t="n">
-        <v>0</v>
-      </c>
-      <c r="N839" t="n">
-        <v>0</v>
-      </c>
-      <c r="O839" t="n">
-        <v>0</v>
-      </c>
-      <c r="P839" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q839" t="n">
-        <v>0</v>
-      </c>
-      <c r="R839" s="2" t="inlineStr"/>
+      <c r="H843" t="n">
+        <v>0</v>
+      </c>
+      <c r="I843" t="n">
+        <v>0</v>
+      </c>
+      <c r="J843" t="n">
+        <v>0</v>
+      </c>
+      <c r="K843" t="n">
+        <v>0</v>
+      </c>
+      <c r="L843" t="n">
+        <v>0</v>
+      </c>
+      <c r="M843" t="n">
+        <v>0</v>
+      </c>
+      <c r="N843" t="n">
+        <v>0</v>
+      </c>
+      <c r="O843" t="n">
+        <v>0</v>
+      </c>
+      <c r="P843" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q843" t="n">
+        <v>0</v>
+      </c>
+      <c r="R843" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -569,7 +569,7 @@
         <v>45348</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         <v>44322</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44761</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45204</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44221</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44937</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>45084</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45162</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44000</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>44435</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45013</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45196</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45239</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>43452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>43510</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>44188</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45099</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>43872</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44322</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>44480</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>44831</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44998</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45049</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45061</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45121</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>45211</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>43389</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>43453</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>43581</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>43873</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44167</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44188</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44410</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>44456</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44547</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44560</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44571</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>44693</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44694</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44706</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>44825</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44832</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45035</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45041</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45089</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45093</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>45105</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45126</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45140</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45153</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45189</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>45197</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45208</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>43355</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>43363</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>43384</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>43385</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>43385</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>43385</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>43389</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43389</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>43403</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43404</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>43404</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>43404</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>43411</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>43413</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>43416</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>43425</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>43427</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>43436</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>43447</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>43452</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>43472</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>43472</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>43472</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>43473</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43494</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>43497</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>43500</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>43501</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43502</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>43532</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>43546</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>43551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>43551</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>43557</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>43566</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>43593</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>43594</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>43601</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         <v>43605</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>43614</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>43628</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>43630</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>43630</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>43630</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>43633</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>43636</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>43649</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>43656</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>43662</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>43664</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>43681</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>43696</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>43698</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>43700</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>43705</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>43714</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>43720</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43731</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43733</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>43734</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43747</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43770</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43780</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43782</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>43788</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>43791</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>43797</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>43798</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>43798</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>43798</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>43798</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>43801</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>43817</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>43819</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>43847</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>43847</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>43858</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>43860</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>43861</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>43861</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>43868</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>43868</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>43872</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>43873</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>43881</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>43881</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>43882</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>43887</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>43887</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>43892</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>43892</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>43893</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>43893</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43894</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43894</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>43895</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>43898</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>43900</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>43903</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43903</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43908</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>43910</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>43915</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>43918</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>43921</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>43921</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>43922</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>43923</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>43923</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>43923</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>43923</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>43923</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>43923</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>43924</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>43949</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>43965</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>43965</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>43969</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>43978</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>43983</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>43983</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>43983</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>43983</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>43983</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>43983</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>43993</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>43999</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44000</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>44000</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>44006</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>44012</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44020</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44022</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>44036</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>44067</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>44069</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>44069</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>44070</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44081</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>44085</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>44085</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44085</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44085</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>44089</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>44090</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>44092</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44092</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44092</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44092</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>44092</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44092</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>44092</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>44093</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>44097</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44097</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>44103</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>44103</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44104</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44113</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44116</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44116</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>44118</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>44119</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44119</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>44120</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44123</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>44124</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>44127</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44127</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44131</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>44154</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44154</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44154</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>44159</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44165</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44166</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>44168</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>44174</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>44188</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>44188</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>44188</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>44188</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>44188</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>44209</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>44217</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>44218</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44224</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>44237</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>44244</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17379,7 +17379,7 @@
         <v>44244</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>44249</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>44264</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>44274</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>44281</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>44286</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>44291</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44292</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>44292</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44299</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>44302</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>44316</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44316</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>44316</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>44316</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>44316</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>44322</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>44322</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>44322</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>44330</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>44333</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44333</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44336</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>44336</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>44337</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44341</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>44344</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44344</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>44358</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>44362</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>44364</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>44368</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>44369</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>44369</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44370</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44370</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44370</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>44370</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>44376</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44377</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>44377</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>44386</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>44386</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>44387</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>44393</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44397</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44404</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>44405</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>44406</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>44413</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44420</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44431</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44434</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>44435</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>44435</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44439</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44439</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44441</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44447</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44449</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>44452</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44453</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44456</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>44456</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>44459</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44459</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44460</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44462</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44470</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>44476</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44477</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44477</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44482</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44482</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44502</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44503</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>44508</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>44515</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>44516</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>44516</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>44533</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>44536</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>44543</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>44550</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>44552</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>44560</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>44560</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44572</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44579</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44579</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44581</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>44590</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>44599</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44600</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>44602</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>44603</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>44616</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>44643</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>44652</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>44656</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>44658</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>44662</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>44680</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>44685</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>44687</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>44687</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>44700</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>44701</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44706</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>44706</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24098,7 +24098,7 @@
         <v>44708</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44711</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>44715</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44720</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44720</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>44725</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>44729</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>44730</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>44730</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44730</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>44730</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44731</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>44731</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>44731</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>44731</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>44731</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>44731</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44731</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44731</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25271,7 +25271,7 @@
         <v>44730</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>44731</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>44731</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>44731</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>44731</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>44732</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>44733</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44741</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44743</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44771</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44771</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>44771</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>44785</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44789</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>44805</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>44805</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>44809</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26300,7 +26300,7 @@
         <v>44809</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>44811</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44813</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44817</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44817</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>44819</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44820</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44820</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>44820</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>44825</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>44825</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26977,7 +26977,7 @@
         <v>44825</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44826</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>44826</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44827</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44827</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>44827</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>44827</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44830</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44831</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>44831</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>44831</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>44832</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44833</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44833</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>44841</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>44844</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>44844</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>44844</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>44844</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>44844</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>44845</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44848</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>44851</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>44851</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44852</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44853</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44854</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>44859</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44859</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>44859</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28807,7 +28807,7 @@
         <v>44859</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>44859</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44859</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>44861</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>44862</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>44867</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>44867</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>44869</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>44869</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44869</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44872</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>44872</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>44872</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44872</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>44874</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>44879</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30094,7 +30094,7 @@
         <v>44879</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>44879</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>44880</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>44883</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>44883</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>44886</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>44887</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>44890</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>44890</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44893</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>44893</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>44893</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44895</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44900</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>44903</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>44907</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44907</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>44915</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>44915</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31237,7 +31237,7 @@
         <v>44915</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>44916</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>44923</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>44929</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>44929</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>44929</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44937</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31651,7 +31651,7 @@
         <v>44938</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44939</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>44942</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>44950</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>44957</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>44957</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>44958</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>44958</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44960</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>44960</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>44960</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>44960</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>44960</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>44963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44964</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>44965</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44966</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>44967</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44970</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>44970</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44970</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32913,7 +32913,7 @@
         <v>44971</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>44972</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>44974</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>44978</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>44981</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>44994</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>44994</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>44998</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45002</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>45002</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>45002</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45013</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>45021</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>45030</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45034</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45034</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>45034</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45034</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45043</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34056,7 +34056,7 @@
         <v>45043</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>45043</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>45044</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45044</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>45044</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>45050</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45051</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>45051</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34552,7 +34552,7 @@
         <v>45054</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45055</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>45055</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45056</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45058</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>45058</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34909,7 +34909,7 @@
         <v>45058</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45062</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>45062</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>45062</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35157,7 +35157,7 @@
         <v>45062</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>45063</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45063</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45063</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35405,7 +35405,7 @@
         <v>45063</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>45063</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
         <v>45063</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45063</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45063</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35710,7 +35710,7 @@
         <v>45068</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45068</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         <v>45068</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>45068</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>45068</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36005,7 +36005,7 @@
         <v>45069</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45069</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45070</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45070</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45070</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45070</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>45071</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45078</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45079</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45079</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45082</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45082</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45084</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45086</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45086</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>45089</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45091</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37059,7 +37059,7 @@
         <v>45093</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45093</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>45093</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45098</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>45098</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>45098</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45098</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45099</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37555,7 +37555,7 @@
         <v>45099</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>45099</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45099</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37741,7 +37741,7 @@
         <v>45099</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>45099</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45099</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>45103</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45105</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>45105</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>45106</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>45107</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>45107</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>45110</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38341,7 +38341,7 @@
         <v>45110</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38398,7 +38398,7 @@
         <v>45110</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>45110</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>45112</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45112</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>45112</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>45113</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>45113</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45114</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45114</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45114</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45114</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39060,7 +39060,7 @@
         <v>45117</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>45118</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45119</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45119</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45119</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39365,7 +39365,7 @@
         <v>45121</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>45121</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>45125</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
         <v>45125</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45125</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45126</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45127</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>45128</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>45128</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>45128</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>45131</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45131</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45132</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>45134</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40218,7 +40218,7 @@
         <v>45134</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>45134</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>45134</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40404,7 +40404,7 @@
         <v>45134</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>45135</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>45140</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40590,7 +40590,7 @@
         <v>45140</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>45142</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>45148</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45149</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>45149</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>45149</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45152</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45152</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>45152</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>45155</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>45156</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>45156</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>45156</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>45156</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45156</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45161</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41676,7 +41676,7 @@
         <v>45161</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45161</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41800,7 +41800,7 @@
         <v>45161</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>45161</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>45161</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>45163</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>45163</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45166</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45166</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45166</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45166</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>45166</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>45167</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>45167</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         <v>45167</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45167</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45168</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>45168</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45168</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45168</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>45168</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45168</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>45170</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>45170</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45170</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>45170</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43402,7 +43402,7 @@
         <v>45170</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45170</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43526,7 +43526,7 @@
         <v>45173</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43588,7 +43588,7 @@
         <v>45174</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45175</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43712,7 +43712,7 @@
         <v>45175</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45175</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>45176</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45177</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45177</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>45177</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45177</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>45177</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>45180</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45180</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44327,7 +44327,7 @@
         <v>45182</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>45182</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45182</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45183</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45184</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45184</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44699,7 +44699,7 @@
         <v>45184</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45187</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>45187</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>45187</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44947,7 +44947,7 @@
         <v>45187</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>45187</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>45187</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>45188</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         <v>45188</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45188</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>45188</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45381,7 +45381,7 @@
         <v>45188</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>45188</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45505,7 +45505,7 @@
         <v>45189</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45562,7 +45562,7 @@
         <v>45191</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45191</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45191</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>45191</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45810,7 +45810,7 @@
         <v>45191</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>45191</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45934,7 +45934,7 @@
         <v>45191</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45996,7 +45996,7 @@
         <v>45191</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46058,7 +46058,7 @@
         <v>45194</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46115,7 +46115,7 @@
         <v>45195</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46172,7 +46172,7 @@
         <v>45196</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46234,7 +46234,7 @@
         <v>45196</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46296,7 +46296,7 @@
         <v>45198</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45198</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>45198</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45198</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>45198</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>45198</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46668,7 +46668,7 @@
         <v>45198</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45198</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46792,7 +46792,7 @@
         <v>45198</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>45202</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45202</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45202</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45202</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45202</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45204</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>45204</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45205</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>45205</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45205</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45205</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47531,7 +47531,7 @@
         <v>45208</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         <v>45208</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>45208</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47717,7 +47717,7 @@
         <v>45208</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47779,7 +47779,7 @@
         <v>45208</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47836,7 +47836,7 @@
         <v>45210</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
         <v>45210</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45212</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45212</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48084,7 +48084,7 @@
         <v>45212</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45215</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45215</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45216</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45217</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45218</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45219</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>45219</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48565,7 +48565,7 @@
         <v>45219</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         <v>45219</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48689,7 +48689,7 @@
         <v>45223</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48746,7 +48746,7 @@
         <v>45224</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>45225</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45225</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>45225</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45225</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49046,7 +49046,7 @@
         <v>45226</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>45226</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45226</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45230</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49294,7 +49294,7 @@
         <v>45230</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45230</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49413,7 +49413,7 @@
         <v>45230</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45230</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>45236</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45236</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>45237</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>45239</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45243</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49837,7 +49837,7 @@
         <v>45243</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>45243</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         <v>45244</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50008,7 +50008,7 @@
         <v>45246</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45246</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50122,7 +50122,7 @@
         <v>45246</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>45247</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45247</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45247</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50365,7 +50365,7 @@
         <v>45249</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50422,7 +50422,7 @@
         <v>45253</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45253</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>45253</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>45253</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45253</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>45254</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50794,7 +50794,7 @@
         <v>45254</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50851,7 +50851,7 @@
         <v>45257</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>45257</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>45257</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45258</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51084,7 +51084,7 @@
         <v>45260</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>45265</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51198,7 +51198,7 @@
         <v>45273</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51317,7 +51317,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45280</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51488,7 +51488,7 @@
         <v>45288</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51545,7 +51545,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>45297</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45301</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>45301</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51778,7 +51778,7 @@
         <v>45302</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45303</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>45307</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51954,7 +51954,7 @@
         <v>45308</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52011,7 +52011,7 @@
         <v>45313</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>45313</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52145,7 +52145,7 @@
         <v>45313</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45313</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52259,7 +52259,7 @@
         <v>45317</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52316,7 +52316,7 @@
         <v>45317</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>45317</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45321</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52487,7 +52487,7 @@
         <v>45321</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
         <v>45335</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52658,7 +52658,7 @@
         <v>45335</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52715,7 +52715,7 @@
         <v>45337</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>45345</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52822,14 +52822,14 @@
     <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
-          <t>A 8162-2024</t>
+          <t>A 8170-2024</t>
         </is>
       </c>
       <c r="B839" s="1" t="n">
         <v>45349</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52847,133 +52847,133 @@
         </is>
       </c>
       <c r="G839" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H839" t="n">
+        <v>0</v>
+      </c>
+      <c r="I839" t="n">
+        <v>0</v>
+      </c>
+      <c r="J839" t="n">
+        <v>0</v>
+      </c>
+      <c r="K839" t="n">
+        <v>0</v>
+      </c>
+      <c r="L839" t="n">
+        <v>0</v>
+      </c>
+      <c r="M839" t="n">
+        <v>0</v>
+      </c>
+      <c r="N839" t="n">
+        <v>0</v>
+      </c>
+      <c r="O839" t="n">
+        <v>0</v>
+      </c>
+      <c r="P839" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q839" t="n">
+        <v>0</v>
+      </c>
+      <c r="R839" s="2" t="inlineStr"/>
+    </row>
+    <row r="840" ht="15" customHeight="1">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>A 8162-2024</t>
+        </is>
+      </c>
+      <c r="B840" s="1" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C840" s="1" t="n">
+        <v>45353</v>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="G840" t="n">
         <v>6.9</v>
       </c>
-      <c r="H839" t="n">
-        <v>0</v>
-      </c>
-      <c r="I839" t="n">
-        <v>0</v>
-      </c>
-      <c r="J839" t="n">
-        <v>0</v>
-      </c>
-      <c r="K839" t="n">
-        <v>0</v>
-      </c>
-      <c r="L839" t="n">
-        <v>0</v>
-      </c>
-      <c r="M839" t="n">
-        <v>0</v>
-      </c>
-      <c r="N839" t="n">
-        <v>0</v>
-      </c>
-      <c r="O839" t="n">
-        <v>0</v>
-      </c>
-      <c r="P839" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q839" t="n">
-        <v>0</v>
-      </c>
-      <c r="R839" s="2" t="inlineStr"/>
-      <c r="U839">
+      <c r="H840" t="n">
+        <v>0</v>
+      </c>
+      <c r="I840" t="n">
+        <v>0</v>
+      </c>
+      <c r="J840" t="n">
+        <v>0</v>
+      </c>
+      <c r="K840" t="n">
+        <v>0</v>
+      </c>
+      <c r="L840" t="n">
+        <v>0</v>
+      </c>
+      <c r="M840" t="n">
+        <v>0</v>
+      </c>
+      <c r="N840" t="n">
+        <v>0</v>
+      </c>
+      <c r="O840" t="n">
+        <v>0</v>
+      </c>
+      <c r="P840" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q840" t="n">
+        <v>0</v>
+      </c>
+      <c r="R840" s="2" t="inlineStr"/>
+      <c r="U840">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/knärot/A 8162-2024 karta knärot.png", "A 8162-2024")</f>
         <v/>
       </c>
-      <c r="V839">
+      <c r="V840">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomål/A 8162-2024 FSC-klagomål.docx", "A 8162-2024")</f>
         <v/>
       </c>
-      <c r="W839">
+      <c r="W840">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomålsmail/A 8162-2024 FSC-klagomål mail.docx", "A 8162-2024")</f>
         <v/>
       </c>
-      <c r="X839">
+      <c r="X840">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsyn/A 8162-2024 tillsynsbegäran.docx", "A 8162-2024")</f>
         <v/>
       </c>
-      <c r="Y839">
+      <c r="Y840">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsynsmail/A 8162-2024 tillsynsbegäran mail.docx", "A 8162-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="840" ht="15" customHeight="1">
-      <c r="A840" t="inlineStr">
-        <is>
-          <t>A 8172-2024</t>
-        </is>
-      </c>
-      <c r="B840" s="1" t="n">
-        <v>45349</v>
-      </c>
-      <c r="C840" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="D840" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="E840" t="inlineStr">
-        <is>
-          <t>LUDVIKA</t>
-        </is>
-      </c>
-      <c r="F840" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="G840" t="n">
-        <v>2</v>
-      </c>
-      <c r="H840" t="n">
-        <v>0</v>
-      </c>
-      <c r="I840" t="n">
-        <v>0</v>
-      </c>
-      <c r="J840" t="n">
-        <v>0</v>
-      </c>
-      <c r="K840" t="n">
-        <v>0</v>
-      </c>
-      <c r="L840" t="n">
-        <v>0</v>
-      </c>
-      <c r="M840" t="n">
-        <v>0</v>
-      </c>
-      <c r="N840" t="n">
-        <v>0</v>
-      </c>
-      <c r="O840" t="n">
-        <v>0</v>
-      </c>
-      <c r="P840" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q840" t="n">
-        <v>0</v>
-      </c>
-      <c r="R840" s="2" t="inlineStr"/>
-    </row>
     <row r="841" ht="15" customHeight="1">
       <c r="A841" t="inlineStr">
         <is>
-          <t>A 8170-2024</t>
+          <t>A 8172-2024</t>
         </is>
       </c>
       <c r="B841" s="1" t="n">
         <v>45349</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         </is>
       </c>
       <c r="G841" t="n">
-        <v>5.7</v>
+        <v>2</v>
       </c>
       <c r="H841" t="n">
         <v>0</v>
@@ -53035,7 +53035,7 @@
         <v>45349</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53097,7 +53097,7 @@
         <v>45350</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -569,7 +569,7 @@
         <v>45348</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         <v>44322</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>44761</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>45204</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>44221</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>44937</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>45084</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45162</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44000</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>44435</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>45013</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>45196</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45239</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>43452</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>43510</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>44188</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>45099</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>43872</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>44322</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>44480</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>44831</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>44998</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45049</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>45061</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>45121</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>45211</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>43389</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>43453</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>43581</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>43873</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44167</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44188</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44410</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>44456</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44547</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44560</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>44571</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>44693</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44694</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44706</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>44825</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44832</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>44888</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>45035</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45041</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45089</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>45093</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>45105</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45126</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45140</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45153</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45189</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>45197</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>45208</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>43355</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>43363</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>43384</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>43385</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>43385</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>43385</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>43389</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>43389</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>43403</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>43404</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>43404</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>43404</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>43411</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>43411</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
         <v>43413</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>43416</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>43425</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>43427</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>43436</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>43447</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>43451</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>43452</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>43472</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>43472</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>43472</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>43473</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>43494</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>43497</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>43500</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>43501</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>43502</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>43531</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>43532</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>43546</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>43551</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>43551</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>43557</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>43566</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
